--- a/tool/kintone-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/kintone-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC5448C0-1444-469B-BAB1-E724F0589DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{114682C6-97ED-4793-B5B4-6D17619C96F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6120" windowWidth="23040" windowHeight="6120" xr2:uid="{A9B54438-BA04-420D-A352-9E7E332C0F5A}"/>
+    <workbookView xWindow="0" yWindow="6120" windowWidth="23040" windowHeight="6120" xr2:uid="{63E21072-0E5C-491C-AFC8-F6F143A74999}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -25,15 +25,15 @@
     <sheet name="2.9 環境設定（マスター）" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（一括実行）'!$A$1:$F$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.2 実行（アプリデータ作成）'!$A$1:$F$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2.3 実行（アプリデータ集計）'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2.4 実行（アラート集計）'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2.5 実行（投稿）'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 ログ'!$A$1:$F$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 環境設定（共通）'!$A$1:$F$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'2.8 環境設定（グループ別）'!$A$1:$F$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（マスター）'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（一括実行）'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.2 実行（アプリデータ作成）'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2.3 実行（アプリデータ集計）'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2.4 実行（アラート集計）'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2.5 実行（投稿）'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 ログ'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 環境設定（共通）'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'2.8 環境設定（グループ別）'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（マスター）'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">一覧!$A$1:$C$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="154">
   <si>
     <t>通番</t>
   </si>
@@ -117,25 +117,32 @@
     <t>区分</t>
   </si>
   <si>
+    <t>入力値</t>
+  </si>
+  <si>
     <t>操作</t>
   </si>
   <si>
-    <t>期待結果</t>
+    <t>期待値</t>
   </si>
   <si>
     <t>参照</t>
   </si>
   <si>
-    <t>結果</t>
+    <t>実施結果</t>
   </si>
   <si>
     <t>正常系</t>
   </si>
   <si>
-    <t>対象日と対象のグループを入力して、実行を押します。</t>
-  </si>
-  <si>
-    <t>選んだ日付と、選んだグループの処理が実行され、状態が成功または警告と表示されます。</t>
+    <t>対象日：2026-09-01
+対象のグループ：ok</t>
+  </si>
+  <si>
+    <t>実行を押します。</t>
+  </si>
+  <si>
+    <t>処理ごとの状態：成功または警告</t>
   </si>
   <si>
     <t>画面設計 3.1、処理フロー 2.1</t>
@@ -144,22 +151,26 @@
     <t/>
   </si>
   <si>
-    <t>業務日誌のチェックを外して、実行を押します。</t>
-  </si>
-  <si>
-    <t>業務日誌は「スキップ」と表示され、ほかの処理は実行されます。</t>
+    <t>対象日：2026-09-01
+対象のグループ：ok
+アプリデータ作成-業務日誌：なし</t>
+  </si>
+  <si>
+    <t>業務日誌の状態：スキップ
+ほかの処理の状態：成功、警告、失敗のいずれか</t>
   </si>
   <si>
     <t>実行が終わったあと、ログ欄を確認します。</t>
   </si>
   <si>
-    <t>実行結果のログが表示されます。ログの出力先に実行ログが保存されます。</t>
-  </si>
-  <si>
-    <t>処理の「開く」を押します。</t>
-  </si>
-  <si>
-    <t>処理の出力先のフォルダ、または対象のスレッドが開きます。</t>
+    <t>ログ欄：一括実行 完了
+ログの出力先：logs フォルダがある</t>
+  </si>
+  <si>
+    <t>すべての行の「開く」を押します。</t>
+  </si>
+  <si>
+    <t>開いた画面：各処理の出力先のフォルダ、または対象のスレッド</t>
   </si>
   <si>
     <t>画面設計 3.1</t>
@@ -168,127 +179,129 @@
     <t>異常系</t>
   </si>
   <si>
-    <t>対象日を空にして、実行を押します。</t>
-  </si>
-  <si>
-    <t>「対象日 を設定してください。」と表示され、処理は実行されません。</t>
+    <t>対象日：空
+対象のグループ：ok</t>
+  </si>
+  <si>
+    <t>メッセージ：「対象日 を設定してください」
+処理：実行されない</t>
   </si>
   <si>
     <t>実行が終わったあと、処理ごとの状態を確認します。</t>
   </si>
   <si>
-    <t>処理ごとに、成功、警告、失敗、スキップのいずれかが表示されます。</t>
-  </si>
-  <si>
-    <t>異常のクライアント（ng）で、対象日と対象のグループを入力して、実行を押します。</t>
-  </si>
-  <si>
-    <t>業務日誌の状態に失敗と表示され、後続の処理も実行されます。</t>
-  </si>
-  <si>
-    <t>業務日誌の対象日と対象のグループを入力して、実行を押します。</t>
-  </si>
-  <si>
-    <t>状態が成功または警告と表示され、集計用データが作られます。</t>
+    <t>処理ごとの状態：成功、警告、失敗、スキップのいずれか</t>
+  </si>
+  <si>
+    <t>対象日：2026-09-01
+対象のグループ：ng</t>
+  </si>
+  <si>
+    <t>業務日誌の状態：失敗
+後続の処理：実行される</t>
+  </si>
+  <si>
+    <t>業務日誌の実行を押します。</t>
+  </si>
+  <si>
+    <t>状態：成功または警告
+集計用データ：作られる</t>
   </si>
   <si>
     <t>画面設計 3.2、処理フロー 2.2</t>
   </si>
   <si>
-    <t>業務日誌の実行が終わったあと、開くを押します。</t>
-  </si>
-  <si>
-    <t>作成したデータのフォルダが開きます。</t>
+    <t>業務日誌の「開く」を押します。</t>
+  </si>
+  <si>
+    <t>開いた画面：作成したデータのフォルダ</t>
   </si>
   <si>
     <t>画面設計 3.2</t>
   </si>
   <si>
-    <t>パルスサーベイの対象日と対象のグループを入力して、実行を押します。</t>
+    <t>パルスサーベイの実行を押します。</t>
   </si>
   <si>
     <t>画面設計 3.2、処理フロー 2.3</t>
   </si>
   <si>
-    <t>パルスサーベイの実行が終わったあと、開くを押します。</t>
-  </si>
-  <si>
-    <t>業務日誌の対象日を空にして、実行を押します。</t>
-  </si>
-  <si>
-    <t>異常のクライアント（ng）で、業務日誌の対象日と対象のグループを入力して、実行を押します。</t>
-  </si>
-  <si>
-    <t>状態に失敗と表示されます。</t>
-  </si>
-  <si>
-    <t>異常のクライアント（ng）で、パルスサーベイの対象日と対象のグループを入力して、実行を押します。</t>
-  </si>
-  <si>
-    <t>状態が成功または警告と表示され、統合データが作られます。</t>
+    <t>パルスサーベイの「開く」を押します。</t>
+  </si>
+  <si>
+    <t>状態：失敗</t>
+  </si>
+  <si>
+    <t>状態：成功または警告
+統合データ：作られる</t>
   </si>
   <si>
     <t>画面設計 3.3、処理フロー 2.4</t>
   </si>
   <si>
-    <t>実行が終わったあと、開くを押します。</t>
-  </si>
-  <si>
-    <t>統合したデータのフォルダが開きます。</t>
+    <t>開くを押します。</t>
+  </si>
+  <si>
+    <t>開いた画面：統合したデータのフォルダ</t>
   </si>
   <si>
     <t>画面設計 3.3</t>
   </si>
   <si>
-    <t>状態が成功または警告と表示され、アラート結果（Excel と JSON）が作られます。</t>
+    <t>状態：成功または警告
+アラート結果：作られる</t>
   </si>
   <si>
     <t>画面設計 3.4、処理フロー 2.5</t>
   </si>
   <si>
-    <t>検知結果のフォルダが開きます。</t>
+    <t>開いた画面：検知結果のフォルダ</t>
   </si>
   <si>
     <t>画面設計 3.4</t>
   </si>
   <si>
-    <t>状態が成功または警告と表示され、投稿先のスレッドにコメントが投稿されます。</t>
+    <t>状態：成功または警告
+投稿：投稿先のスレッドにコメントが投稿される</t>
   </si>
   <si>
     <t>画面設計 3.4、処理フロー 2.6</t>
   </si>
   <si>
-    <t>対象のスレッドが、ブラウザで開きます。</t>
-  </si>
-  <si>
-    <t>投稿の対象日を空にして、実行を押します。</t>
+    <t>開いた画面：対象のスレッド（ブラウザ）</t>
   </si>
   <si>
     <t>ログのファイルがない状態で、すべて削除を押します。</t>
   </si>
   <si>
-    <t>削除対象のログファイルがないことが表示され、処理は終わります。</t>
+    <t>メッセージ：「削除対象のログファイルがありません」</t>
   </si>
   <si>
     <t>画面設計 3.5、処理フロー 2.7</t>
   </si>
   <si>
-    <t>ログのファイルがある状態で、すべて削除を押し、確認で「いいえ」を選びます。</t>
-  </si>
-  <si>
-    <t>何も削除されず、ログのファイルは残ります。</t>
-  </si>
-  <si>
-    <t>ログのファイルがある状態で、すべて削除を押し、確認で「はい」を選びます。</t>
-  </si>
-  <si>
-    <t>ログのファイルがすべて削除されます。</t>
-  </si>
-  <si>
-    <t>対象のグループで 1 つのグループを選びます。</t>
-  </si>
-  <si>
-    <t>そのグループの実行ログだけが表示されます。</t>
+    <t>確認：いいえ</t>
+  </si>
+  <si>
+    <t>ログのファイルがある状態で、すべて削除を押します。</t>
+  </si>
+  <si>
+    <t>ログのファイル：残る</t>
+  </si>
+  <si>
+    <t>確認：はい</t>
+  </si>
+  <si>
+    <t>ログのファイル：すべて削除される</t>
+  </si>
+  <si>
+    <t>対象のグループ：すべて、ok、ng</t>
+  </si>
+  <si>
+    <t>対象のグループを選びます。</t>
+  </si>
+  <si>
+    <t>表示されるログ：「すべて」では ok と ng の両方、「ok」では ok のログだけ、「ng」では ng のログだけ</t>
   </si>
   <si>
     <t>画面設計 3.5</t>
@@ -297,22 +310,30 @@
     <t>処理のラジオボタンを切り替えます。</t>
   </si>
   <si>
-    <t>選んだ処理のログだけが表示されます。</t>
-  </si>
-  <si>
-    <t>基本設定の値を変えて、保存を押します。</t>
-  </si>
-  <si>
-    <t>変えた値が保存され、画面の表示が保存後の内容に更新されます。</t>
+    <t>表示されるログ：選んだ処理のログだけ（ok と ng の両方）</t>
+  </si>
+  <si>
+    <t>基本設定：%BASE_PATH%clients_test</t>
+  </si>
+  <si>
+    <t>保存を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：変えた値が保存される
+画面の表示：保存後の内容に更新</t>
   </si>
   <si>
     <t>画面設計 3.6、処理フロー 2.8</t>
   </si>
   <si>
-    <t>基本設定の値を変えたあと、再読込を押します。</t>
-  </si>
-  <si>
-    <t>保存されている値で入力欄が表示し直され、変えた内容は消えます。</t>
+    <t>基本設定：%BASE_PATH%clients_tmp</t>
+  </si>
+  <si>
+    <t>再読込を押します。</t>
+  </si>
+  <si>
+    <t>入力欄：保存されている値
+変えた内容：消える</t>
   </si>
   <si>
     <t>画面設計 3.6、処理フロー 2.9</t>
@@ -321,7 +342,7 @@
     <t>アプリデータ集計の列定義で、行を選んで削除を押します。</t>
   </si>
   <si>
-    <t>選んだ行が削除されます。</t>
+    <t>表：選んだ行が削除される</t>
   </si>
   <si>
     <t>画面設計 3.6、処理フロー 2.10</t>
@@ -330,76 +351,107 @@
     <t>アプリデータ集計の列定義で、追加を押します。</t>
   </si>
   <si>
-    <t>表の末尾に、空の行が追加されます。</t>
+    <t>表：末尾に空の行が追加される</t>
   </si>
   <si>
     <t>画面設計 3.6、処理フロー 2.11</t>
   </si>
   <si>
-    <t>新規作成を押し、既存のグループと同じ名前を入力します。</t>
-  </si>
-  <si>
-    <t>「「（入力した名前）」は既に存在します。」と表示され、グループは追加されません。</t>
+    <t>対象のグループ：ok
+新しい名前：ok（既存のグループ名）</t>
+  </si>
+  <si>
+    <t>新規作成を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「（入力した名前）は既に存在します。」
+一覧：追加されない</t>
   </si>
   <si>
     <t>画面設計 3.7、処理フロー 2.12</t>
   </si>
   <si>
-    <t>新規作成を押し、新しい名前を入力します。</t>
-  </si>
-  <si>
-    <t>名前が対象のグループの一覧に追加され、選ばれます。</t>
+    <t>対象のグループ：ok
+新しい名前：AggNew</t>
+  </si>
+  <si>
+    <t>一覧：名前が追加され、選ばれる</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+新しい名前：AggUnsaved</t>
   </si>
   <si>
     <t>新規作成直後の、まだ保存していないグループを選び、コピーを押します。</t>
   </si>
   <si>
-    <t>「コピー元のグループが存在しません」と表示され、コピーは行われません。</t>
+    <t>メッセージ：「コピー元のグループが存在しません」
+コピー：行われない</t>
   </si>
   <si>
     <t>画面設計 3.7、処理フロー 2.13</t>
   </si>
   <si>
-    <t>保存済みのグループを選び、コピーを押して、新しい名前を入力します。</t>
-  </si>
-  <si>
-    <t>新しいグループが一覧に 1 つだけ追加され、選ばれます。設定ファイルと Excel ファイルがコピーされます。</t>
-  </si>
-  <si>
-    <t>入力欄の値を変えて、保存を押します。</t>
-  </si>
-  <si>
-    <t>値が設定ファイルに保存され、画面の表示が保存後の内容に更新されます。</t>
+    <t>対象のグループ：ok
+新しい名前：AggCopy</t>
+  </si>
+  <si>
+    <t>保存済みのグループを選び、コピーを押します。</t>
+  </si>
+  <si>
+    <t>一覧：AggCopy が選ばれる
+設定ファイル：AggCopy.bat が作られる
+Excel ファイル：AggCopy.xlsx が作られる</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+認証情報：saved</t>
+  </si>
+  <si>
+    <t>設定ファイル：値が保存される
+画面の表示：保存後の内容に更新</t>
   </si>
   <si>
     <t>画面設計 3.7、処理フロー 2.14</t>
   </si>
   <si>
-    <t>入力欄の値を変えたあと、再読込を押します。</t>
+    <t>対象のグループ：ok
+認証情報：tmp</t>
   </si>
   <si>
     <t>画面設計 3.7、処理フロー 2.15</t>
   </si>
   <si>
-    <t>正しい接続情報で、テスト接続（認証情報）を押します。</t>
-  </si>
-  <si>
-    <t>状態に成功と表示されます。</t>
+    <t>対象のグループ：ok、入力なし（保存されている接続情報）</t>
+  </si>
+  <si>
+    <t>テスト接続（認証情報）を押します。</t>
+  </si>
+  <si>
+    <t>状態：成功</t>
   </si>
   <si>
     <t>画面設計 3.7、処理フロー 2.16</t>
   </si>
   <si>
-    <t>正しいアプリIDで、テスト接続（業務日誌）を押します。</t>
+    <t>対象のグループ：ok
+対象アプリID（業務日誌）：180</t>
+  </si>
+  <si>
+    <t>テスト接続（業務日誌）を押します。</t>
   </si>
   <si>
     <t>画面設計 3.7、処理フロー 2.18</t>
   </si>
   <si>
-    <t>正しい投稿先で、テスト投稿（投稿先）を押します。</t>
-  </si>
-  <si>
-    <t>状態に成功と表示され、テスト用のコメントが投稿されます。</t>
+    <t>対象のグループ：ok、入力なし（保存されている投稿先）</t>
+  </si>
+  <si>
+    <t>テスト投稿（投稿先）を押します。</t>
+  </si>
+  <si>
+    <t>状態：成功
+テスト用のコメント：投稿される</t>
   </si>
   <si>
     <t>画面設計 3.7、処理フロー 2.20</t>
@@ -408,37 +460,46 @@
     <t>10</t>
   </si>
   <si>
+    <t>対象のグループ：ok</t>
+  </si>
+  <si>
     <t>新規作成を押したあと、キャンセルを押します。</t>
   </si>
   <si>
-    <t>一覧は変わりません。</t>
+    <t>一覧：変わらない</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>認証情報のサブドメインを空にして、テスト接続（認証情報）を押します。</t>
-  </si>
-  <si>
-    <t>状態に失敗と表示され、接続は行われません。</t>
+    <t>対象のグループ：ok
+認証情報：空</t>
+  </si>
+  <si>
+    <t>状態：失敗
+接続：行われない</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>業務日誌の対象アプリIDを空にして、テスト接続（業務日誌）を押します。</t>
+    <t>対象のグループ：ok
+対象アプリID（業務日誌）：空</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>投稿先スペースIDを空にして、テスト投稿（投稿先）を押します。</t>
-  </si>
-  <si>
-    <t>状態に失敗と表示され、投稿は行われません。</t>
-  </si>
-  <si>
-    <t>誤ったパスワードで、テスト接続（認証情報）を押します。</t>
+    <t>対象のグループ：ok
+投稿先：空</t>
+  </si>
+  <si>
+    <t>状態：失敗
+投稿：行われない</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+認証情報：wrong-password</t>
   </si>
   <si>
     <t>スケジュールの表で、行を選んで削除を押します。</t>
@@ -447,28 +508,32 @@
     <t>画面設計 3.8、処理フロー 2.24</t>
   </si>
   <si>
-    <t>科目名などを変えて、保存を押します。</t>
-  </si>
-  <si>
-    <t>値が保存され、画面の表示が保存後の内容に更新されます。</t>
+    <t>対象のグループ：ok
+スケジュールの科目名：テスト科目</t>
+  </si>
+  <si>
+    <t>画面の表示：保存後の内容（テスト科目）が表示される</t>
   </si>
   <si>
     <t>画面設計 3.8、処理フロー 2.21</t>
   </si>
   <si>
-    <t>値を変えたあと、再読込を押します。</t>
-  </si>
-  <si>
-    <t>保存されている値で表が表示し直され、変えた内容は消えます。</t>
+    <t>対象のグループ：ok
+スケジュールの科目名：一時</t>
+  </si>
+  <si>
+    <t>表：保存されている値で表示し直される
+変えた内容：消える</t>
   </si>
   <si>
     <t>画面設計 3.8、処理フロー 2.22</t>
   </si>
   <si>
-    <t>対象のグループを選び、同期実行（ユーザー）を押します。</t>
-  </si>
-  <si>
-    <t>状態に成功と表示され、受講生一覧のシートにユーザーマスターの内容が書き込まれます。</t>
+    <t>同期実行（ユーザー）を押します。</t>
+  </si>
+  <si>
+    <t>状態：成功
+受講生一覧：ユーザーマスターの内容が書き込まれる</t>
   </si>
   <si>
     <t>画面設計 3.8、処理フロー 2.23</t>
@@ -480,7 +545,7 @@
     <t>画面設計 3.8、処理フロー 2.25</t>
   </si>
   <si>
-    <t>異常のクライアント（ng）で、対象のグループを選び、同期実行（ユーザー）を押します。</t>
+    <t>対象のグループ：ng</t>
   </si>
 </sst>
 </file>
@@ -879,7 +944,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2479FD1C-3C29-42FB-AB38-C6419EB805D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8503AA-4286-4AC5-B82B-5BD4CC0477C7}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -999,26 +1064,27 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10" xr:uid="{2479FD1C-3C29-42FB-AB38-C6419EB805D6}"/>
+  <autoFilter ref="A1:C10" xr:uid="{3F8503AA-4286-4AC5-B82B-5BD4CC0477C7}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{539E378F-F098-4A50-851E-7AC0A923A361}">
-  <dimension ref="A1:F7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C8F919F-0983-4E9D-BDF9-7F536E4991B2}">
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="18.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1037,148 +1103,170 @@
       <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+        <v>141</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>134</v>
+        <v>85</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+        <v>144</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="198" x14ac:dyDescent="0.45">
+        <v>147</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="90" x14ac:dyDescent="0.45">
+        <v>150</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="90" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="216" x14ac:dyDescent="0.45">
+        <v>152</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="90" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>150</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7" xr:uid="{539E378F-F098-4A50-851E-7AC0A923A361}"/>
+  <autoFilter ref="A1:G7" xr:uid="{8C8F919F-0983-4E9D-BDF9-7F536E4991B2}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AF8B2BE-B2B1-4AB3-B28A-891B33AD1D80}">
-  <dimension ref="A1:F8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1671BA7-A2E6-4984-8B9C-D0C21FBF192C}">
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="18.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1197,168 +1285,193 @@
       <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="198" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+      <c r="G3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8" xr:uid="{9AF8B2BE-B2B1-4AB3-B28A-891B33AD1D80}"/>
+  <autoFilter ref="A1:G8" xr:uid="{B1671BA7-A2E6-4984-8B9C-D0C21FBF192C}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AC26C90-AB1C-4522-A692-2B3D4C08518B}">
-  <dimension ref="A1:F8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D89FC7C0-B9BF-4CCF-B705-8FA855AD7D7C}">
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="18.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1377,168 +1490,193 @@
       <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>50</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>53</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+        <v>55</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>53</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="216" x14ac:dyDescent="0.45">
+        <v>50</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="216" x14ac:dyDescent="0.45">
+        <v>50</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>31</v>
+        <v>55</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8" xr:uid="{8AC26C90-AB1C-4522-A692-2B3D4C08518B}"/>
+  <autoFilter ref="A1:G8" xr:uid="{D89FC7C0-B9BF-4CCF-B705-8FA855AD7D7C}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74976D0C-7EB2-4972-80D7-2D9FF0645492}">
-  <dimension ref="A1:F4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{734A5082-8015-4B81-A371-44E46A1D1F27}">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="18.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1557,88 +1695,101 @@
       <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="90" x14ac:dyDescent="0.45">
+      <c r="G2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+      <c r="G3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
+        <v>59</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4" xr:uid="{74976D0C-7EB2-4972-80D7-2D9FF0645492}"/>
+  <autoFilter ref="A1:G4" xr:uid="{734A5082-8015-4B81-A371-44E46A1D1F27}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B97949-8DCA-4CA1-A89F-9B964A89EFFE}">
-  <dimension ref="A1:F4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B641D08D-2777-44BF-8922-4E3D5D28A16F}">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="18.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1657,88 +1808,101 @@
       <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="198" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="90" x14ac:dyDescent="0.45">
+      <c r="G2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+      <c r="G3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
+        <v>64</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4" xr:uid="{B9B97949-8DCA-4CA1-A89F-9B964A89EFFE}"/>
+  <autoFilter ref="A1:G4" xr:uid="{B641D08D-2777-44BF-8922-4E3D5D28A16F}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCCACEC6-CF5C-4EE7-A6BF-68B8A5E96B7C}">
-  <dimension ref="A1:F4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC1D5B38-B163-4A8C-9D8F-D597E97B8D8C}">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="18.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1757,88 +1921,101 @@
       <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="90" x14ac:dyDescent="0.45">
+      <c r="G2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
+        <v>68</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4" xr:uid="{CCCACEC6-CF5C-4EE7-A6BF-68B8A5E96B7C}"/>
+  <autoFilter ref="A1:G4" xr:uid="{BC1D5B38-B163-4A8C-9D8F-D597E97B8D8C}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0E7C195-3971-4D70-8924-AC8426717AAC}">
-  <dimension ref="A1:F6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE8C4112-F345-4342-B189-2B222C0709A4}">
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="18.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1857,128 +2034,147 @@
       <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+      <c r="G2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+        <v>72</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>72</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="90" x14ac:dyDescent="0.45">
+      <c r="G5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>31</v>
+      <c r="G6" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F6" xr:uid="{A0E7C195-3971-4D70-8924-AC8426717AAC}"/>
+  <autoFilter ref="A1:G6" xr:uid="{FE8C4112-F345-4342-B189-2B222C0709A4}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE2891E5-04A4-49CA-97F8-426E35A3E209}">
-  <dimension ref="A1:F5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A720794C-0945-412C-A5BB-3145C89534A8}">
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="18.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1997,13 +2193,16 @@
       <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>84</v>
@@ -2015,90 +2214,103 @@
         <v>86</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+        <v>91</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>94</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>31</v>
+        <v>97</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5" xr:uid="{DE2891E5-04A4-49CA-97F8-426E35A3E209}"/>
+  <autoFilter ref="A1:G5" xr:uid="{A720794C-0945-412C-A5BB-3145C89534A8}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77F5C991-C991-4C5B-8998-BA7521B10AB2}">
-  <dimension ref="A1:F15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18B2D07C-5F2F-4E6A-AC0A-652A9295802A}">
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="18.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2117,289 +2329,334 @@
       <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="198" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+        <v>101</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+        <v>101</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="234" x14ac:dyDescent="0.45">
+        <v>107</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>107</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+        <v>113</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+        <v>119</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="108" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
+      <c r="E12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="G12" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="162" x14ac:dyDescent="0.45">
-      <c r="A12" s="2" t="s">
+      <c r="E13" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="G13" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="162" x14ac:dyDescent="0.45">
-      <c r="A13" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="E14" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="144" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+      <c r="G14" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>31</v>
+        <v>119</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F15" xr:uid="{77F5C991-C991-4C5B-8998-BA7521B10AB2}"/>
+  <autoFilter ref="A1:G15" xr:uid="{18B2D07C-5F2F-4E6A-AC0A-652A9295802A}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/kintone-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/kintone-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{114682C6-97ED-4793-B5B4-6D17619C96F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{095AE2AC-37FB-4C19-9174-1B24C93A2A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6120" windowWidth="23040" windowHeight="6120" xr2:uid="{63E21072-0E5C-491C-AFC8-F6F143A74999}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{17058579-AFA6-4650-89BA-FF77F1D31473}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="174">
   <si>
     <t>通番</t>
   </si>
@@ -133,181 +133,272 @@
   </si>
   <si>
     <t>正常系</t>
+  </si>
+  <si>
+    <t>対象日：2026-09-01
+対象のグループ：ok
+アプリデータ作成-業務日誌：あり
+アプリデータ作成-パルスサーベイ：あり
+アプリデータ集計-業務日誌・パルスサーベイ：あり
+アラート集計-業務日誌・パルスサーベイ：あり
+アラート集計-投稿：あり</t>
+  </si>
+  <si>
+    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>状態（アプリデータ作成-業務日誌）：成功または警告
+状態（アプリデータ作成-パルスサーベイ）：成功または警告
+状態（アプリデータ集計-業務日誌・パルスサーベイ）：成功または警告
+状態（アラート集計-業務日誌・パルスサーベイ）：成功または警告
+状態（アラート集計-投稿）：成功または警告</t>
+  </si>
+  <si>
+    <t>画面設計：3.1
+処理フロー：2.1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>対象日：2026-09-01
+対象のグループ：ok
+アプリデータ作成-業務日誌：なし
+アプリデータ作成-パルスサーベイ：あり
+アプリデータ集計-業務日誌・パルスサーベイ：あり
+アラート集計-業務日誌・パルスサーベイ：あり
+アラート集計-投稿：あり</t>
+  </si>
+  <si>
+    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「アプリデータ作成-業務日誌」のチェックを外して、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>状態（アプリデータ作成-業務日誌）：スキップ
+状態（アプリデータ作成-パルスサーベイ）：成功、警告、失敗のいずれか
+状態（アプリデータ集計-業務日誌・パルスサーベイ）：成功、警告、失敗のいずれか
+状態（アラート集計-業務日誌・パルスサーベイ）：成功、警告、失敗のいずれか
+状態（アラート集計-投稿）：成功、警告、失敗のいずれか</t>
+  </si>
+  <si>
+    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行」を押して実行が終わったあと、ログ欄を確認します。</t>
+  </si>
+  <si>
+    <t>ログ：一括実行 完了
+ログの出力先：logs フォルダがある</t>
+  </si>
+  <si>
+    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行」を押して実行が終わったあと、すべての行の「開く」を押します。</t>
+  </si>
+  <si>
+    <t>開いた画面：各処理の出力先のフォルダ、または対象のスレッド</t>
+  </si>
+  <si>
+    <t>画面設計：3.1</t>
+  </si>
+  <si>
+    <t>異常系</t>
+  </si>
+  <si>
+    <t>対象日：空
+対象のグループ：ok
+アプリデータ作成-業務日誌：あり
+アプリデータ作成-パルスサーベイ：あり
+アプリデータ集計-業務日誌・パルスサーベイ：あり
+アラート集計-業務日誌・パルスサーベイ：あり
+アラート集計-投稿：あり</t>
+  </si>
+  <si>
+    <t>「対象日」を空にして、「対象のグループ」を選んだあと、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「対象日 を設定してください」</t>
+  </si>
+  <si>
+    <t>状態（アプリデータ作成-業務日誌）：成功、警告、失敗、スキップのいずれか
+状態（アプリデータ作成-パルスサーベイ）：成功、警告、失敗、スキップのいずれか
+状態（アプリデータ集計-業務日誌・パルスサーベイ）：成功、警告、失敗、スキップのいずれか
+状態（アラート集計-業務日誌・パルスサーベイ）：成功、警告、失敗、スキップのいずれか
+状態（アラート集計-投稿）：成功、警告、失敗、スキップのいずれか</t>
+  </si>
+  <si>
+    <t>対象日：2026-09-01
+対象のグループ：ng
+アプリデータ作成-業務日誌：あり
+アプリデータ作成-パルスサーベイ：あり
+アプリデータ集計-業務日誌・パルスサーベイ：あり
+アラート集計-業務日誌・パルスサーベイ：あり
+アラート集計-投稿：あり</t>
+  </si>
+  <si>
+    <t>状態（アプリデータ作成-業務日誌）：失敗
+後続の処理：実行される</t>
   </si>
   <si>
     <t>対象日：2026-09-01
 対象のグループ：ok</t>
   </si>
   <si>
-    <t>実行を押します。</t>
-  </si>
-  <si>
-    <t>処理ごとの状態：成功または警告</t>
-  </si>
-  <si>
-    <t>画面設計 3.1、処理フロー 2.1</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>対象日：2026-09-01
-対象のグループ：ok
-アプリデータ作成-業務日誌：なし</t>
-  </si>
-  <si>
-    <t>業務日誌の状態：スキップ
-ほかの処理の状態：成功、警告、失敗のいずれか</t>
-  </si>
-  <si>
-    <t>実行が終わったあと、ログ欄を確認します。</t>
-  </si>
-  <si>
-    <t>ログ欄：一括実行 完了
-ログの出力先：logs フォルダがある</t>
-  </si>
-  <si>
-    <t>すべての行の「開く」を押します。</t>
-  </si>
-  <si>
-    <t>開いた画面：各処理の出力先のフォルダ、または対象のスレッド</t>
-  </si>
-  <si>
-    <t>画面設計 3.1</t>
-  </si>
-  <si>
-    <t>異常系</t>
+    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（業務日誌）」を押します。</t>
+  </si>
+  <si>
+    <t>状態：成功または警告
+集計用データ：作られる</t>
+  </si>
+  <si>
+    <t>画面設計：3.2
+処理フロー：2.2</t>
+  </si>
+  <si>
+    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（業務日誌）」を押して実行が終わったあと、業務日誌の「開く」を押します。</t>
+  </si>
+  <si>
+    <t>開いた画面：作成したデータのフォルダ</t>
+  </si>
+  <si>
+    <t>画面設計：3.2</t>
+  </si>
+  <si>
+    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（パルスサーベイ）」を押します。</t>
+  </si>
+  <si>
+    <t>画面設計：3.2
+処理フロー：2.3</t>
+  </si>
+  <si>
+    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（パルスサーベイ）」を押して実行が終わったあと、パルスサーベイの「開く」を押します。</t>
   </si>
   <si>
     <t>対象日：空
 対象のグループ：ok</t>
   </si>
   <si>
-    <t>メッセージ：「対象日 を設定してください」
-処理：実行されない</t>
-  </si>
-  <si>
-    <t>実行が終わったあと、処理ごとの状態を確認します。</t>
-  </si>
-  <si>
-    <t>処理ごとの状態：成功、警告、失敗、スキップのいずれか</t>
+    <t>「対象日」を空にして、「対象のグループ」を選んだあと、「実行（業務日誌）」を押します。</t>
   </si>
   <si>
     <t>対象日：2026-09-01
 対象のグループ：ng</t>
   </si>
   <si>
-    <t>業務日誌の状態：失敗
-後続の処理：実行される</t>
-  </si>
-  <si>
-    <t>業務日誌の実行を押します。</t>
-  </si>
-  <si>
-    <t>状態：成功または警告
-集計用データ：作られる</t>
-  </si>
-  <si>
-    <t>画面設計 3.2、処理フロー 2.2</t>
-  </si>
-  <si>
-    <t>業務日誌の「開く」を押します。</t>
-  </si>
-  <si>
-    <t>開いた画面：作成したデータのフォルダ</t>
-  </si>
-  <si>
-    <t>画面設計 3.2</t>
-  </si>
-  <si>
-    <t>パルスサーベイの実行を押します。</t>
-  </si>
-  <si>
-    <t>画面設計 3.2、処理フロー 2.3</t>
-  </si>
-  <si>
-    <t>パルスサーベイの「開く」を押します。</t>
-  </si>
-  <si>
     <t>状態：失敗</t>
+  </si>
+  <si>
+    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（業務日誌）」、「実行（パルスサーベイ）」の順に押して実行が終わったあと、「実行」を押します。</t>
   </si>
   <si>
     <t>状態：成功または警告
 統合データ：作られる</t>
   </si>
   <si>
-    <t>画面設計 3.3、処理フロー 2.4</t>
-  </si>
-  <si>
-    <t>開くを押します。</t>
+    <t>画面設計：3.3
+処理フロー：2.4</t>
+  </si>
+  <si>
+    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（業務日誌）」、「実行（パルスサーベイ）」の順に押して実行が終わったあと、「実行」を押して実行が終わったあと、「開く」を押します。</t>
   </si>
   <si>
     <t>開いた画面：統合したデータのフォルダ</t>
   </si>
   <si>
-    <t>画面設計 3.3</t>
+    <t>画面設計：3.3</t>
+  </si>
+  <si>
+    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（業務日誌）」、「実行（パルスサーベイ）」、「実行」の順に押して実行が終わったあと、「実行（業務日誌・パルスサーベイ）」を押します。</t>
   </si>
   <si>
     <t>状態：成功または警告
 アラート結果：作られる</t>
   </si>
   <si>
-    <t>画面設計 3.4、処理フロー 2.5</t>
+    <t>画面設計：3.4
+処理フロー：2.5</t>
+  </si>
+  <si>
+    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（業務日誌）」、「実行（パルスサーベイ）」、「実行」の順に押し、「実行（業務日誌・パルスサーベイ）」を押して実行が終わったあと、「開く」を押します。</t>
   </si>
   <si>
     <t>開いた画面：検知結果のフォルダ</t>
   </si>
   <si>
-    <t>画面設計 3.4</t>
+    <t>画面設計：3.4</t>
+  </si>
+  <si>
+    <t>「対象日」を空にして、「対象のグループ」を選んだあと、「実行（業務日誌・パルスサーベイ）」を押します。</t>
+  </si>
+  <si>
+    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（業務日誌）」、「実行（パルスサーベイ）」、「実行」、「実行（業務日誌・パルスサーベイ）」の順に押して実行が終わったあと、「実行（投稿）」を押します。</t>
   </si>
   <si>
     <t>状態：成功または警告
 投稿：投稿先のスレッドにコメントが投稿される</t>
   </si>
   <si>
-    <t>画面設計 3.4、処理フロー 2.6</t>
+    <t>画面設計：3.4
+処理フロー：2.6</t>
+  </si>
+  <si>
+    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（業務日誌）」、「実行（パルスサーベイ）」、「実行」、「実行（業務日誌・パルスサーベイ）」の順に押して実行が終わったあと、「実行（投稿）」を押して実行が終わったあと、「開く」を押します。</t>
   </si>
   <si>
     <t>開いた画面：対象のスレッド（ブラウザ）</t>
   </si>
   <si>
-    <t>ログのファイルがない状態で、すべて削除を押します。</t>
+    <t>「対象日」を空にして、「対象のグループ」を選んだあと、「実行（投稿）」を押します。</t>
+  </si>
+  <si>
+    <t>対象のグループ：すべて
+処理：アプリデータ作成-業務日誌</t>
+  </si>
+  <si>
+    <t>ログのファイルがない状態で、「すべて削除」を押します。</t>
   </si>
   <si>
     <t>メッセージ：「削除対象のログファイルがありません」</t>
   </si>
   <si>
-    <t>画面設計 3.5、処理フロー 2.7</t>
-  </si>
-  <si>
-    <t>確認：いいえ</t>
-  </si>
-  <si>
-    <t>ログのファイルがある状態で、すべて削除を押します。</t>
+    <t>画面設計：3.5
+処理フロー：2.7</t>
+  </si>
+  <si>
+    <t>対象のグループ：すべて
+確認：いいえ
+処理：アプリデータ作成-業務日誌</t>
+  </si>
+  <si>
+    <t>ログのファイルがある状態で、「すべて削除」を押し、確認で「いいえ」を押します。</t>
   </si>
   <si>
     <t>ログのファイル：残る</t>
   </si>
   <si>
-    <t>確認：はい</t>
+    <t>対象のグループ：すべて
+確認：はい
+処理：アプリデータ作成-業務日誌</t>
+  </si>
+  <si>
+    <t>ログのファイルがある状態で、「すべて削除」を押し、確認で「はい」を押します。</t>
   </si>
   <si>
     <t>ログのファイル：すべて削除される</t>
   </si>
   <si>
-    <t>対象のグループ：すべて、ok、ng</t>
-  </si>
-  <si>
-    <t>対象のグループを選びます。</t>
-  </si>
-  <si>
-    <t>表示されるログ：「すべて」では ok と ng の両方、「ok」では ok のログだけ、「ng」では ng のログだけ</t>
-  </si>
-  <si>
-    <t>画面設計 3.5</t>
-  </si>
-  <si>
-    <t>処理のラジオボタンを切り替えます。</t>
+    <t>対象のグループ：すべて、ok
+処理：アプリデータ作成-業務日誌</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を選びます。</t>
+  </si>
+  <si>
+    <t>表示されるログ：「すべて」では ok と ng の両方、「ok」では ok のログだけ</t>
+  </si>
+  <si>
+    <t>画面設計：3.5</t>
+  </si>
+  <si>
+    <t>対象のグループ：すべて、ok、ng、すべて
+処理：アプリデータ作成-業務日誌、アプリデータ作成-パルスサーベイ、アプリデータ集計-業務日誌・パルスサーベイ、アラート集計-業務日誌・パルスサーベイ、アラート集計-投稿、マスター同期</t>
+  </si>
+  <si>
+    <t>「アプリデータ作成-業務日誌」のラジオボタンを押し、「対象のグループ」を切り替えたあと、残りの処理のラジオボタンを上から順に切り替えます。</t>
   </si>
   <si>
     <t>表示されるログ：選んだ処理のログだけ（ok と ng の両方）</t>
@@ -316,87 +407,91 @@
     <t>基本設定：%BASE_PATH%clients_test</t>
   </si>
   <si>
-    <t>保存を押します。</t>
+    <t>「基本設定」を入力して、「保存」を押します。</t>
   </si>
   <si>
     <t>設定ファイル：変えた値が保存される
 画面の表示：保存後の内容に更新</t>
   </si>
   <si>
-    <t>画面設計 3.6、処理フロー 2.8</t>
+    <t>画面設計：3.6
+処理フロー：2.8</t>
   </si>
   <si>
     <t>基本設定：%BASE_PATH%clients_tmp</t>
   </si>
   <si>
-    <t>再読込を押します。</t>
+    <t>「基本設定」を入力して、「再読込」を押します。</t>
   </si>
   <si>
     <t>入力欄：保存されている値
 変えた内容：消える</t>
   </si>
   <si>
-    <t>画面設計 3.6、処理フロー 2.9</t>
-  </si>
-  <si>
-    <t>アプリデータ集計の列定義で、行を選んで削除を押します。</t>
+    <t>画面設計：3.6
+処理フロー：2.9</t>
+  </si>
+  <si>
+    <t>アプリデータ集計の列定義で、行を選んで「削除（アプリデータ集計の列定義）」を押します。</t>
   </si>
   <si>
     <t>表：選んだ行が削除される</t>
   </si>
   <si>
-    <t>画面設計 3.6、処理フロー 2.10</t>
-  </si>
-  <si>
-    <t>アプリデータ集計の列定義で、追加を押します。</t>
+    <t>画面設計：3.6
+処理フロー：2.10</t>
+  </si>
+  <si>
+    <t>アプリデータ集計の列定義で、「追加（アプリデータ集計の列定義）」を押します。</t>
   </si>
   <si>
     <t>表：末尾に空の行が追加される</t>
   </si>
   <si>
-    <t>画面設計 3.6、処理フロー 2.11</t>
+    <t>画面設計：3.6
+処理フロー：2.11</t>
   </si>
   <si>
     <t>対象のグループ：ok
-新しい名前：ok（既存のグループ名）</t>
-  </si>
-  <si>
-    <t>新規作成を押します。</t>
-  </si>
-  <si>
-    <t>メッセージ：「（入力した名前）は既に存在します。」
-一覧：追加されない</t>
-  </si>
-  <si>
-    <t>画面設計 3.7、処理フロー 2.12</t>
+グループ名：ok（既存のグループ名）</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を選んだあと、「新規作成」を押し、「グループ名」を入力して「OK」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「（入力した名前）は既に存在します。」</t>
+  </si>
+  <si>
+    <t>画面設計：3.7
+処理フロー：2.12</t>
   </si>
   <si>
     <t>対象のグループ：ok
-新しい名前：AggNew</t>
+グループ名：AggNew</t>
   </si>
   <si>
     <t>一覧：名前が追加され、選ばれる</t>
   </si>
   <si>
     <t>対象のグループ：ok
-新しい名前：AggUnsaved</t>
-  </si>
-  <si>
-    <t>新規作成直後の、まだ保存していないグループを選び、コピーを押します。</t>
-  </si>
-  <si>
-    <t>メッセージ：「コピー元のグループが存在しません」
-コピー：行われない</t>
-  </si>
-  <si>
-    <t>画面設計 3.7、処理フロー 2.13</t>
+グループ名：AggUnsaved</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を選んだあと、「新規作成」を押し、「グループ名」を入力して「OK」を押したあと、「コピー」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「コピー元のグループが存在しません」</t>
+  </si>
+  <si>
+    <t>画面設計：3.7
+処理フロー：2.13</t>
   </si>
   <si>
     <t>対象のグループ：ok
-新しい名前：AggCopy</t>
-  </si>
-  <si>
-    <t>保存済みのグループを選び、コピーを押します。</t>
+グループ名：AggCopy</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を選んだあと、「コピー」を押し、「グループ名」を入力して「OK」を押します。</t>
   </si>
   <si>
     <t>一覧：AggCopy が選ばれる
@@ -405,56 +500,67 @@
   </si>
   <si>
     <t>対象のグループ：ok
-認証情報：saved</t>
+サブドメイン：saved</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を選んだあと、「サブドメイン」を入力して、「保存」を押します。</t>
   </si>
   <si>
     <t>設定ファイル：値が保存される
 画面の表示：保存後の内容に更新</t>
   </si>
   <si>
-    <t>画面設計 3.7、処理フロー 2.14</t>
+    <t>画面設計：3.7
+処理フロー：2.14</t>
   </si>
   <si>
     <t>対象のグループ：ok
-認証情報：tmp</t>
-  </si>
-  <si>
-    <t>画面設計 3.7、処理フロー 2.15</t>
+サブドメイン：tmp</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を選んだあと、「サブドメイン」を入力して、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>画面設計：3.7
+処理フロー：2.15</t>
   </si>
   <si>
     <t>対象のグループ：ok、入力なし（保存されている接続情報）</t>
   </si>
   <si>
-    <t>テスト接続（認証情報）を押します。</t>
+    <t>「対象のグループ」を選んだあと、「再読込」を押して、「テスト接続（認証情報）」を押します。</t>
   </si>
   <si>
     <t>状態：成功</t>
   </si>
   <si>
-    <t>画面設計 3.7、処理フロー 2.16</t>
+    <t>画面設計：3.7
+処理フロー：2.16</t>
   </si>
   <si>
     <t>対象のグループ：ok
 対象アプリID（業務日誌）：180</t>
   </si>
   <si>
-    <t>テスト接続（業務日誌）を押します。</t>
-  </si>
-  <si>
-    <t>画面設計 3.7、処理フロー 2.18</t>
+    <t>「対象のグループ」を選んだあと、「対象アプリID（業務日誌）」を入力して、「テスト接続（業務日誌）」を押します。</t>
+  </si>
+  <si>
+    <t>画面設計：3.7
+処理フロー：2.18</t>
   </si>
   <si>
     <t>対象のグループ：ok、入力なし（保存されている投稿先）</t>
   </si>
   <si>
-    <t>テスト投稿（投稿先）を押します。</t>
+    <t>「対象のグループ」を選んだあと、「テスト投稿（投稿先）」を押します。</t>
   </si>
   <si>
     <t>状態：成功
 テスト用のコメント：投稿される</t>
   </si>
   <si>
-    <t>画面設計 3.7、処理フロー 2.20</t>
+    <t>画面設計：3.7
+処理フロー：2.20</t>
   </si>
   <si>
     <t>10</t>
@@ -463,21 +569,20 @@
     <t>対象のグループ：ok</t>
   </si>
   <si>
-    <t>新規作成を押したあと、キャンセルを押します。</t>
-  </si>
-  <si>
-    <t>一覧：変わらない</t>
+    <t>「対象のグループ」を選んだあと、「新規作成」を押したあと、「キャンセル」を押します。</t>
+  </si>
+  <si>
+    <t>ダイアログが閉じる</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
     <t>対象のグループ：ok
-認証情報：空</t>
-  </si>
-  <si>
-    <t>状態：失敗
-接続：行われない</t>
+サブドメイン：空</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を選んだあと、「サブドメイン」を空にして、「テスト接続（認証情報）」を押します。</t>
   </si>
   <si>
     <t>12</t>
@@ -487,62 +592,74 @@
 対象アプリID（業務日誌）：空</t>
   </si>
   <si>
+    <t>「対象のグループ」を選んだあと、「対象アプリID（業務日誌）」を空にして、「テスト接続（業務日誌）」を押します。</t>
+  </si>
+  <si>
     <t>13</t>
   </si>
   <si>
     <t>対象のグループ：ok
-投稿先：空</t>
-  </si>
-  <si>
-    <t>状態：失敗
-投稿：行われない</t>
+投稿先スペースID：空</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を選んだあと、「投稿先スペースID」を空にして、「テスト投稿（投稿先）」を押します。</t>
   </si>
   <si>
     <t>対象のグループ：ok
-認証情報：wrong-password</t>
-  </si>
-  <si>
-    <t>スケジュールの表で、行を選んで削除を押します。</t>
-  </si>
-  <si>
-    <t>画面設計 3.8、処理フロー 2.24</t>
+パスワード：wrong-password</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を選んだあと、「パスワード」を入力して、「テスト接続（認証情報）」を押します。</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を選んだあと、スケジュールの1行目の「削除（スケジュール）」を押します。</t>
+  </si>
+  <si>
+    <t>画面設計：3.8
+処理フロー：2.24</t>
   </si>
   <si>
     <t>対象のグループ：ok
-スケジュールの科目名：テスト科目</t>
+科目名：テスト科目</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を選んだあと、スケジュールの1行目の「科目名」を入力して、「保存」を押します。</t>
   </si>
   <si>
     <t>画面の表示：保存後の内容（テスト科目）が表示される</t>
   </si>
   <si>
-    <t>画面設計 3.8、処理フロー 2.21</t>
+    <t>画面設計：3.8
+処理フロー：2.21</t>
   </si>
   <si>
     <t>対象のグループ：ok
-スケジュールの科目名：一時</t>
+科目名：一時</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を選んだあと、スケジュールの1行目の「科目名」を入力して、「再読込」を押します。</t>
   </si>
   <si>
     <t>表：保存されている値で表示し直される
 変えた内容：消える</t>
   </si>
   <si>
-    <t>画面設計 3.8、処理フロー 2.22</t>
-  </si>
-  <si>
-    <t>同期実行（ユーザー）を押します。</t>
-  </si>
-  <si>
-    <t>状態：成功
-受講生一覧：ユーザーマスターの内容が書き込まれる</t>
-  </si>
-  <si>
-    <t>画面設計 3.8、処理フロー 2.23</t>
-  </si>
-  <si>
-    <t>スケジュールの表で、追加を押します。</t>
-  </si>
-  <si>
-    <t>画面設計 3.8、処理フロー 2.25</t>
+    <t>画面設計：3.8
+処理フロー：2.22</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を選んだあと、「同期実行（ユーザー）」を押します。</t>
+  </si>
+  <si>
+    <t>画面設計：3.8
+処理フロー：2.23</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を選んだあと、「追加（スケジュール）」を押します。</t>
+  </si>
+  <si>
+    <t>画面設計：3.8
+処理フロー：2.25</t>
   </si>
   <si>
     <t>対象のグループ：ng</t>
@@ -944,13 +1061,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8503AA-4286-4AC5-B82B-5BD4CC0477C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C015A2D3-954B-4595-8D14-83C00173E75D}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="3" width="10.69921875" customWidth="1"/>
+    <col min="2" max="3" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
@@ -1064,23 +1180,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10" xr:uid="{3F8503AA-4286-4AC5-B82B-5BD4CC0477C7}"/>
+  <autoFilter ref="A1:C10" xr:uid="{C015A2D3-954B-4595-8D14-83C00173E75D}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C8F919F-0983-4E9D-BDF9-7F536E4991B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E9B7A57-7138-48C8-9DB4-5EDE4CC04FA9}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="18.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1107,7 +1221,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1115,22 +1229,22 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1138,22 +1252,22 @@
         <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>85</v>
+        <v>162</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1161,22 +1275,22 @@
         <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>89</v>
+        <v>166</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1184,22 +1298,22 @@
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1207,62 +1321,60 @@
         <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{8C8F919F-0983-4E9D-BDF9-7F536E4991B2}"/>
+  <autoFilter ref="A1:G7" xr:uid="{9E9B7A57-7138-48C8-9DB4-5EDE4CC04FA9}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1671BA7-A2E6-4984-8B9C-D0C21FBF192C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4873671F-2C5D-4A5E-8B36-7790E4D43065}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="18.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1289,7 +1401,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1312,7 +1424,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1323,10 +1435,10 @@
         <v>34</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>32</v>
@@ -1335,7 +1447,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1346,10 +1458,10 @@
         <v>29</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>32</v>
@@ -1358,7 +1470,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1369,33 +1481,33 @@
         <v>29</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>32</v>
@@ -1404,21 +1516,21 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>32</v>
@@ -1427,21 +1539,21 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>32</v>
@@ -1451,23 +1563,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{B1671BA7-A2E6-4984-8B9C-D0C21FBF192C}"/>
+  <autoFilter ref="A1:G8" xr:uid="{4873671F-2C5D-4A5E-8B36-7790E4D43065}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D89FC7C0-B9BF-4CCF-B705-8FA855AD7D7C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA52E2D5-A6A3-4782-9A92-6E0073018A4B}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="18.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1494,7 +1604,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1502,22 +1612,22 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="324" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1525,22 +1635,22 @@
         <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1548,22 +1658,22 @@
         <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="342" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1571,108 +1681,106 @@
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="G8" s="2" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{D89FC7C0-B9BF-4CCF-B705-8FA855AD7D7C}"/>
+  <autoFilter ref="A1:G8" xr:uid="{AA52E2D5-A6A3-4782-9A92-6E0073018A4B}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{734A5082-8015-4B81-A371-44E46A1D1F27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56901CD1-168D-4A09-9291-B6D589973477}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="18.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1699,7 +1807,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="396" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1707,22 +1815,22 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1730,62 +1838,60 @@
         <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{734A5082-8015-4B81-A371-44E46A1D1F27}"/>
+  <autoFilter ref="A1:G4" xr:uid="{56901CD1-168D-4A09-9291-B6D589973477}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B641D08D-2777-44BF-8922-4E3D5D28A16F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C24E788E-3061-4656-9920-E166B4DA38AF}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="18.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1812,7 +1918,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1820,22 +1926,22 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1843,62 +1949,60 @@
         <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{B641D08D-2777-44BF-8922-4E3D5D28A16F}"/>
+  <autoFilter ref="A1:G4" xr:uid="{C24E788E-3061-4656-9920-E166B4DA38AF}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC1D5B38-B163-4A8C-9D8F-D597E97B8D8C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D905974D-916B-4B32-A6E6-1BB4A4CABC0B}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="18.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1925,7 +2029,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1933,22 +2037,22 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1956,62 +2060,60 @@
         <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{BC1D5B38-B163-4A8C-9D8F-D597E97B8D8C}"/>
+  <autoFilter ref="A1:G4" xr:uid="{D905974D-916B-4B32-A6E6-1BB4A4CABC0B}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE8C4112-F345-4342-B189-2B222C0709A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D5552D-0EC2-4CEC-B1E7-7B39707D544F}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="18.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2038,7 +2140,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2046,22 +2148,22 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -2069,22 +2171,22 @@
         <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -2092,22 +2194,22 @@
         <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2115,22 +2217,22 @@
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -2138,39 +2240,37 @@
         <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{FE8C4112-F345-4342-B189-2B222C0709A4}"/>
+  <autoFilter ref="A1:G6" xr:uid="{35D5552D-0EC2-4CEC-B1E7-7B39707D544F}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A720794C-0945-412C-A5BB-3145C89534A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9124780-6F4B-4428-8E4E-EF229C4CD882}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="18.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2205,16 +2305,16 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>33</v>
@@ -2228,22 +2328,22 @@
         <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -2254,19 +2354,19 @@
         <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2277,36 +2377,34 @@
         <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{A720794C-0945-412C-A5BB-3145C89534A8}"/>
+  <autoFilter ref="A1:G5" xr:uid="{C9124780-6F4B-4428-8E4E-EF229C4CD882}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18B2D07C-5F2F-4E6A-AC0A-652A9295802A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B6F8FD-3D00-4EAF-9828-1CC2D13D61EC}">
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="18.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" customWidth="1"/>
+    <col min="3" max="5" width="50.69921875" customWidth="1"/>
+    <col min="6" max="6" width="30.69921875" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2333,7 +2431,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2341,22 +2439,22 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -2364,22 +2462,22 @@
         <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -2387,16 +2485,16 @@
         <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>33</v>
@@ -2410,22 +2508,22 @@
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -2433,22 +2531,22 @@
         <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -2456,22 +2554,22 @@
         <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -2479,22 +2577,22 @@
         <v>28</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -2502,22 +2600,22 @@
         <v>28</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
@@ -2525,138 +2623,138 @@
         <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>133</v>
+        <v>62</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>133</v>
+        <v>62</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>138</v>
+        <v>62</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15" xr:uid="{18B2D07C-5F2F-4E6A-AC0A-652A9295802A}"/>
+  <autoFilter ref="A1:G15" xr:uid="{95B6F8FD-3D00-4EAF-9828-1CC2D13D61EC}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/kintone-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/kintone-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{095AE2AC-37FB-4C19-9174-1B24C93A2A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2381E03E-A093-4F60-B9DD-6D6D93EBAA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{17058579-AFA6-4650-89BA-FF77F1D31473}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F679081C-2DE6-450E-92B4-A9DB47F8917A}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -32,8 +32,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2.5 実行（投稿）'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 ログ'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 環境設定（共通）'!$A$1:$G$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'2.8 環境設定（グループ別）'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（マスター）'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'2.8 環境設定（グループ別）'!$A$1:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（マスター）'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">一覧!$A$1:$C$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="185">
   <si>
     <t>通番</t>
   </si>
@@ -105,7 +105,7 @@
     <t>環境設定（グループ別）</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>9</t>
@@ -144,7 +144,7 @@
 アラート集計-投稿：あり</t>
   </si>
   <si>
-    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行」を押します。</t>
+    <t>「対象日」と「対象のグループ」を設定した後で、「実行」を押します。</t>
   </si>
   <si>
     <t>状態（アプリデータ作成-業務日誌）：成功または警告
@@ -170,7 +170,7 @@
 アラート集計-投稿：あり</t>
   </si>
   <si>
-    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「アプリデータ作成-業務日誌」のチェックを外して、「実行」を押します。</t>
+    <t>「対象日」と「対象のグループ」を設定した後で、「アプリデータ作成-業務日誌」のチェックを外して、「実行」を押します。</t>
   </si>
   <si>
     <t>状態（アプリデータ作成-業務日誌）：スキップ
@@ -180,14 +180,14 @@
 状態（アラート集計-投稿）：成功、警告、失敗のいずれか</t>
   </si>
   <si>
-    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行」を押して実行が終わったあと、ログ欄を確認します。</t>
+    <t>「対象日」と「対象のグループ」を設定した後で、「実行」を押した後で、ログ欄を確認します。</t>
   </si>
   <si>
     <t>ログ：一括実行 完了
 ログの出力先：logs フォルダがある</t>
   </si>
   <si>
-    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行」を押して実行が終わったあと、すべての行の「開く」を押します。</t>
+    <t>「対象日」と「対象のグループ」を設定した後で、「実行」を押した後で、すべての行の「開く」を押します。</t>
   </si>
   <si>
     <t>開いた画面：各処理の出力先のフォルダ、または対象のスレッド</t>
@@ -208,10 +208,7 @@
 アラート集計-投稿：あり</t>
   </si>
   <si>
-    <t>「対象日」を空にして、「対象のグループ」を選んだあと、「実行」を押します。</t>
-  </si>
-  <si>
-    <t>メッセージ：「対象日 を設定してください」</t>
+    <t>メッセージ：「対象日 を設定してください。」</t>
   </si>
   <si>
     <t>状態（アプリデータ作成-業務日誌）：成功、警告、失敗、スキップのいずれか
@@ -238,10 +235,10 @@
 対象のグループ：ok</t>
   </si>
   <si>
-    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（業務日誌）」を押します。</t>
-  </si>
-  <si>
-    <t>状態：成功または警告
+    <t>「対象日」と「対象のグループ」を設定した後で、「実行（業務日誌）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（業務日誌）：成功または警告
 集計用データ：作られる</t>
   </si>
   <si>
@@ -249,7 +246,7 @@
 処理フロー：2.2</t>
   </si>
   <si>
-    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（業務日誌）」を押して実行が終わったあと、業務日誌の「開く」を押します。</t>
+    <t>「対象日」と「対象のグループ」を設定した後で、「実行（業務日誌）」を押した後で、「開く（業務日誌）」を押します。</t>
   </si>
   <si>
     <t>開いた画面：作成したデータのフォルダ</t>
@@ -258,31 +255,35 @@
     <t>画面設計：3.2</t>
   </si>
   <si>
-    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（パルスサーベイ）」を押します。</t>
+    <t>「対象日」と「対象のグループ」を設定した後で、「実行（パルスサーベイ）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（パルスサーベイ）：成功または警告
+集計用データ：作られる</t>
   </si>
   <si>
     <t>画面設計：3.2
 処理フロー：2.3</t>
   </si>
   <si>
-    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（パルスサーベイ）」を押して実行が終わったあと、パルスサーベイの「開く」を押します。</t>
+    <t>「対象日」と「対象のグループ」を設定した後で、「実行（パルスサーベイ）」を押した後で、「開く（パルスサーベイ）」を押します。</t>
   </si>
   <si>
     <t>対象日：空
 対象のグループ：ok</t>
   </si>
   <si>
-    <t>「対象日」を空にして、「対象のグループ」を選んだあと、「実行（業務日誌）」を押します。</t>
-  </si>
-  <si>
     <t>対象日：2026-09-01
 対象のグループ：ng</t>
   </si>
   <si>
-    <t>状態：失敗</t>
-  </si>
-  <si>
-    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（業務日誌）」、「実行（パルスサーベイ）」の順に押して実行が終わったあと、「実行」を押します。</t>
+    <t>状態（業務日誌）：失敗</t>
+  </si>
+  <si>
+    <t>状態（パルスサーベイ）：失敗</t>
+  </si>
+  <si>
+    <t>「実行（業務日誌）」と「実行（パルスサーベイ）」を順に実行し、「対象日」と「対象のグループ」を設定した後で、「実行」を押します。</t>
   </si>
   <si>
     <t>状態：成功または警告
@@ -293,7 +294,7 @@
 処理フロー：2.4</t>
   </si>
   <si>
-    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（業務日誌）」、「実行（パルスサーベイ）」の順に押して実行が終わったあと、「実行」を押して実行が終わったあと、「開く」を押します。</t>
+    <t>「実行（業務日誌）」と「実行（パルスサーベイ）」を順に実行し、「対象日」と「対象のグループ」を設定した後で、「実行」を押した後で、「開く」を押します。</t>
   </si>
   <si>
     <t>開いた画面：統合したデータのフォルダ</t>
@@ -302,10 +303,10 @@
     <t>画面設計：3.3</t>
   </si>
   <si>
-    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（業務日誌）」、「実行（パルスサーベイ）」、「実行」の順に押して実行が終わったあと、「実行（業務日誌・パルスサーベイ）」を押します。</t>
-  </si>
-  <si>
-    <t>状態：成功または警告
+    <t>「実行（業務日誌）」と「実行（パルスサーベイ）」と「実行」を順に実行し、「対象日」と「対象のグループ」を設定した後で、「実行（業務日誌・パルスサーベイ）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（業務日誌・パルスサーベイ）：成功または警告
 アラート結果：作られる</t>
   </si>
   <si>
@@ -313,7 +314,7 @@
 処理フロー：2.5</t>
   </si>
   <si>
-    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（業務日誌）」、「実行（パルスサーベイ）」、「実行」の順に押し、「実行（業務日誌・パルスサーベイ）」を押して実行が終わったあと、「開く」を押します。</t>
+    <t>「実行（業務日誌）」と「実行（パルスサーベイ）」と「実行」を順に実行し、「対象日」と「対象のグループ」を設定した後で、「実行（業務日誌・パルスサーベイ）」を押した後で、「開く（業務日誌・パルスサーベイ）」を押します。</t>
   </si>
   <si>
     <t>開いた画面：検知結果のフォルダ</t>
@@ -322,13 +323,13 @@
     <t>画面設計：3.4</t>
   </si>
   <si>
-    <t>「対象日」を空にして、「対象のグループ」を選んだあと、「実行（業務日誌・パルスサーベイ）」を押します。</t>
-  </si>
-  <si>
-    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（業務日誌）」、「実行（パルスサーベイ）」、「実行」、「実行（業務日誌・パルスサーベイ）」の順に押して実行が終わったあと、「実行（投稿）」を押します。</t>
-  </si>
-  <si>
-    <t>状態：成功または警告
+    <t>「対象日」と「対象のグループ」を設定した後で、「実行（業務日誌・パルスサーベイ）」を押します。</t>
+  </si>
+  <si>
+    <t>「実行（業務日誌）」と「実行（パルスサーベイ）」と「実行」と「実行（業務日誌・パルスサーベイ）」を順に実行し、「対象日」と「対象のグループ」を設定した後で、「実行（投稿）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（投稿）：成功または警告
 投稿：投稿先のスレッドにコメントが投稿される</t>
   </si>
   <si>
@@ -336,13 +337,13 @@
 処理フロー：2.6</t>
   </si>
   <si>
-    <t>「対象日」を入力して、「対象のグループ」を選んだあと、「実行（業務日誌）」、「実行（パルスサーベイ）」、「実行」、「実行（業務日誌・パルスサーベイ）」の順に押して実行が終わったあと、「実行（投稿）」を押して実行が終わったあと、「開く」を押します。</t>
+    <t>「実行（業務日誌）」と「実行（パルスサーベイ）」と「実行」と「実行（業務日誌・パルスサーベイ）」を順に実行し、「対象日」と「対象のグループ」を設定した後で、「実行（投稿）」を押した後で、「開く（投稿）」を押します。</t>
   </si>
   <si>
     <t>開いた画面：対象のスレッド（ブラウザ）</t>
   </si>
   <si>
-    <t>「対象日」を空にして、「対象のグループ」を選んだあと、「実行（投稿）」を押します。</t>
+    <t>「対象日」と「対象のグループ」を設定した後で、「実行（投稿）」を押します。</t>
   </si>
   <si>
     <t>対象のグループ：すべて
@@ -352,7 +353,7 @@
     <t>ログのファイルがない状態で、「すべて削除」を押します。</t>
   </si>
   <si>
-    <t>メッセージ：「削除対象のログファイルがありません」</t>
+    <t>メッセージ：「削除対象のログファイルがありません。」</t>
   </si>
   <si>
     <t>画面設計：3.5
@@ -407,7 +408,7 @@
     <t>基本設定：%BASE_PATH%clients_test</t>
   </si>
   <si>
-    <t>「基本設定」を入力して、「保存」を押します。</t>
+    <t>「基本設定」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
     <t>設定ファイル：変えた値が保存される
@@ -421,7 +422,7 @@
     <t>基本設定：%BASE_PATH%clients_tmp</t>
   </si>
   <si>
-    <t>「基本設定」を入力して、「再読込」を押します。</t>
+    <t>「基本設定」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
     <t>入力欄：保存されている値
@@ -432,10 +433,13 @@
 処理フロー：2.9</t>
   </si>
   <si>
-    <t>アプリデータ集計の列定義で、行を選んで「削除（アプリデータ集計の列定義）」を押します。</t>
-  </si>
-  <si>
-    <t>表：選んだ行が削除される</t>
+    <t>アプリデータ集計の列定義：13行目</t>
+  </si>
+  <si>
+    <t>アプリデータ集計の列定義の13行目の「削除（アプリデータ集計の列定義）」を押します。</t>
+  </si>
+  <si>
+    <t>表：13行目の行が削除される</t>
   </si>
   <si>
     <t>画面設計：3.6
@@ -456,7 +460,7 @@
 グループ名：ok（既存のグループ名）</t>
   </si>
   <si>
-    <t>「対象のグループ」を選んだあと、「新規作成」を押し、「グループ名」を入力して「OK」を押します。</t>
+    <t>「対象のグループ」を設定した後で、「新規作成」を押し、「グループ名」を入力して「OK」を押します。</t>
   </si>
   <si>
     <t>メッセージ：「（入力した名前）は既に存在します。」</t>
@@ -477,10 +481,10 @@
 グループ名：AggUnsaved</t>
   </si>
   <si>
-    <t>「対象のグループ」を選んだあと、「新規作成」を押し、「グループ名」を入力して「OK」を押したあと、「コピー」を押します。</t>
-  </si>
-  <si>
-    <t>メッセージ：「コピー元のグループが存在しません」</t>
+    <t>「対象のグループ」を設定した後で、「新規作成」を押し、「グループ名」を入力して「OK」を押した後で、「コピー」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「コピー元のグループが存在しません。」</t>
   </si>
   <si>
     <t>画面設計：3.7
@@ -491,7 +495,7 @@
 グループ名：AggCopy</t>
   </si>
   <si>
-    <t>「対象のグループ」を選んだあと、「コピー」を押し、「グループ名」を入力して「OK」を押します。</t>
+    <t>「対象のグループ」を設定した後で、「コピー」を押し、「グループ名」を入力して「OK」を押します。</t>
   </si>
   <si>
     <t>一覧：AggCopy が選ばれる
@@ -503,7 +507,7 @@
 サブドメイン：saved</t>
   </si>
   <si>
-    <t>「対象のグループ」を選んだあと、「サブドメイン」を入力して、「保存」を押します。</t>
+    <t>「対象のグループ」と「サブドメイン」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
     <t>設定ファイル：値が保存される
@@ -518,7 +522,7 @@
 サブドメイン：tmp</t>
   </si>
   <si>
-    <t>「対象のグループ」を選んだあと、「サブドメイン」を入力して、「再読込」を押します。</t>
+    <t>「対象のグループ」と「サブドメイン」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
     <t>画面設計：3.7
@@ -528,10 +532,10 @@
     <t>対象のグループ：ok、入力なし（保存されている接続情報）</t>
   </si>
   <si>
-    <t>「対象のグループ」を選んだあと、「再読込」を押して、「テスト接続（認証情報）」を押します。</t>
-  </si>
-  <si>
-    <t>状態：成功</t>
+    <t>「対象のグループ」を設定した後で、「再読込」を押した後で、「テスト接続（認証情報）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（認証情報）：成功</t>
   </si>
   <si>
     <t>画面設計：3.7
@@ -542,7 +546,10 @@
 対象アプリID（業務日誌）：180</t>
   </si>
   <si>
-    <t>「対象のグループ」を選んだあと、「対象アプリID（業務日誌）」を入力して、「テスト接続（業務日誌）」を押します。</t>
+    <t>「対象のグループ」と「対象アプリID（業務日誌）」を設定した後で、「テスト接続（業務日誌）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（業務日誌）：成功</t>
   </si>
   <si>
     <t>画面設計：3.7
@@ -552,10 +559,10 @@
     <t>対象のグループ：ok、入力なし（保存されている投稿先）</t>
   </si>
   <si>
-    <t>「対象のグループ」を選んだあと、「テスト投稿（投稿先）」を押します。</t>
-  </si>
-  <si>
-    <t>状態：成功
+    <t>「対象のグループ」を設定した後で、「テスト投稿」を押します。</t>
+  </si>
+  <si>
+    <t>状態（テスト投稿）：成功
 テスト用のコメント：投稿される</t>
   </si>
   <si>
@@ -569,7 +576,7 @@
     <t>対象のグループ：ok</t>
   </si>
   <si>
-    <t>「対象のグループ」を選んだあと、「新規作成」を押したあと、「キャンセル」を押します。</t>
+    <t>「対象のグループ」を設定した後で、「新規作成」を押した後で、「キャンセル」を押します。</t>
   </si>
   <si>
     <t>ダイアログが閉じる</t>
@@ -582,7 +589,11 @@
 サブドメイン：空</t>
   </si>
   <si>
-    <t>「対象のグループ」を選んだあと、「サブドメイン」を空にして、「テスト接続（認証情報）」を押します。</t>
+    <t>「対象のグループ」と「サブドメイン」を設定した後で、「テスト接続（認証情報）」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「エラーが発生しました: サブドメイン・ログイン名・パスワードをすべて入力してください。」
+状態（認証情報）：失敗</t>
   </si>
   <si>
     <t>12</t>
@@ -592,7 +603,8 @@
 対象アプリID（業務日誌）：空</t>
   </si>
   <si>
-    <t>「対象のグループ」を選んだあと、「対象アプリID（業務日誌）」を空にして、「テスト接続（業務日誌）」を押します。</t>
+    <t>メッセージ：「エラーが発生しました: 対象アプリIDを入力してください。」
+状態（業務日誌）：失敗</t>
   </si>
   <si>
     <t>13</t>
@@ -602,17 +614,34 @@
 投稿先スペースID：空</t>
   </si>
   <si>
-    <t>「対象のグループ」を選んだあと、「投稿先スペースID」を空にして、「テスト投稿（投稿先）」を押します。</t>
+    <t>「対象のグループ」と「投稿先スペースID」を設定した後で、「テスト投稿」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「エラーが発生しました: スペースID／スレッドIDを入力してください。」
+状態（テスト投稿）：失敗</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>対象のグループ：ok
 パスワード：wrong-password</t>
   </si>
   <si>
-    <t>「対象のグループ」を選んだあと、「パスワード」を入力して、「テスト接続（認証情報）」を押します。</t>
-  </si>
-  <si>
-    <t>「対象のグループ」を選んだあと、スケジュールの1行目の「削除（スケジュール）」を押します。</t>
+    <t>「対象のグループ」と「パスワード」を設定した後で、「テスト接続（認証情報）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（認証情報）：失敗</t>
+  </si>
+  <si>
+    <t>メッセージ：「（入力した名前）は既に存在します。」
+一覧：追加されない</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、スケジュールの1行目の「削除（スケジュール）」を押します。</t>
+  </si>
+  <si>
+    <t>表：選んだ行が削除される</t>
   </si>
   <si>
     <t>画面設計：3.8
@@ -623,7 +652,7 @@
 科目名：テスト科目</t>
   </si>
   <si>
-    <t>「対象のグループ」を選んだあと、スケジュールの1行目の「科目名」を入力して、「保存」を押します。</t>
+    <t>「対象のグループ」を設定し、スケジュールの1行目の「科目名」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
     <t>画面の表示：保存後の内容（テスト科目）が表示される</t>
@@ -637,7 +666,7 @@
 科目名：一時</t>
   </si>
   <si>
-    <t>「対象のグループ」を選んだあと、スケジュールの1行目の「科目名」を入力して、「再読込」を押します。</t>
+    <t>「対象のグループ」を設定し、スケジュールの1行目の「科目名」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
     <t>表：保存されている値で表示し直される
@@ -648,14 +677,17 @@
 処理フロー：2.22</t>
   </si>
   <si>
-    <t>「対象のグループ」を選んだあと、「同期実行（ユーザー）」を押します。</t>
+    <t>「対象のグループ」を設定した後で、「同期実行」を押します。</t>
+  </si>
+  <si>
+    <t>状態（同期実行）：成功</t>
   </si>
   <si>
     <t>画面設計：3.8
 処理フロー：2.23</t>
   </si>
   <si>
-    <t>「対象のグループ」を選んだあと、「追加（スケジュール）」を押します。</t>
+    <t>「対象のグループ」を設定した後で、「追加（スケジュール）」を押します。</t>
   </si>
   <si>
     <t>画面設計：3.8
@@ -663,6 +695,14 @@
   </si>
   <si>
     <t>対象のグループ：ng</t>
+  </si>
+  <si>
+    <t>状態（同期実行）：失敗</t>
+  </si>
+  <si>
+    <t>メッセージ：「エラーが発生しました: 対象アプリIDが設定されていません。」
+状態（同期実行）：失敗
+ユーザーマスター：書き込まれない</t>
   </si>
 </sst>
 </file>
@@ -1061,7 +1101,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C015A2D3-954B-4595-8D14-83C00173E75D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86ACF708-E795-405D-82D8-9F96DF75AE8D}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1176,26 +1216,26 @@
         <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10" xr:uid="{C015A2D3-954B-4595-8D14-83C00173E75D}"/>
+  <autoFilter ref="A1:C10" xr:uid="{86ACF708-E795-405D-82D8-9F96DF75AE8D}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E9B7A57-7138-48C8-9DB4-5EDE4CC04FA9}">
-  <dimension ref="A1:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8A28B49-29AC-4AF0-8235-9256E856B8B9}">
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -1229,16 +1269,16 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>33</v>
@@ -1252,16 +1292,16 @@
         <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>33</v>
@@ -1275,22 +1315,22 @@
         <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1298,16 +1338,16 @@
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>33</v>
@@ -1321,22 +1361,22 @@
         <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -1344,38 +1384,61 @@
         <v>42</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>62</v>
+        <v>183</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>33</v>
       </c>
     </row>
+    <row r="8" spans="1:7" ht="324" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{9E9B7A57-7138-48C8-9DB4-5EDE4CC04FA9}"/>
+  <autoFilter ref="A1:G8" xr:uid="{D8A28B49-29AC-4AF0-8235-9256E856B8B9}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4873671F-2C5D-4A5E-8B36-7790E4D43065}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95DCF242-8AC0-40DF-B6A5-B0611851AEEB}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -1504,10 +1567,10 @@
         <v>43</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>32</v>
@@ -1530,7 +1593,7 @@
         <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>32</v>
@@ -1547,13 +1610,13 @@
         <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>32</v>
@@ -1563,22 +1626,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{4873671F-2C5D-4A5E-8B36-7790E4D43065}"/>
+  <autoFilter ref="A1:G8" xr:uid="{95DCF242-8AC0-40DF-B6A5-B0611851AEEB}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA52E2D5-A6A3-4782-9A92-6E0073018A4B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF3AF382-18C0-4D94-8D1B-661362719FCC}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -1604,7 +1667,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1612,22 +1675,22 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="G2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="324" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1635,22 +1698,22 @@
         <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="G3" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1658,13 +1721,13 @@
         <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>57</v>
@@ -1673,7 +1736,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="342" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1681,22 +1744,22 @@
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>58</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="G5" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1707,19 +1770,19 @@
         <v>59</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -1727,22 +1790,22 @@
         <v>42</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -1750,10 +1813,10 @@
         <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>62</v>
@@ -1766,22 +1829,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{AA52E2D5-A6A3-4782-9A92-6E0073018A4B}"/>
+  <autoFilter ref="A1:G8" xr:uid="{DF3AF382-18C0-4D94-8D1B-661362719FCC}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56901CD1-168D-4A09-9291-B6D589973477}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B185A71B-3A5C-4B56-9651-50BDD14AE1C0}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -1807,7 +1870,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="396" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1815,7 +1878,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>63</v>
@@ -1830,7 +1893,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="360" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1838,7 +1901,7 @@
         <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>66</v>
@@ -1853,7 +1916,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1864,10 +1927,10 @@
         <v>59</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>65</v>
@@ -1877,22 +1940,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{56901CD1-168D-4A09-9291-B6D589973477}"/>
+  <autoFilter ref="A1:G4" xr:uid="{B185A71B-3A5C-4B56-9651-50BDD14AE1C0}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C24E788E-3061-4656-9920-E166B4DA38AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D836FA1-E7B9-4208-977A-E3DEFD2FF48A}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -1926,7 +1989,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>69</v>
@@ -1949,7 +2012,7 @@
         <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>72</v>
@@ -1964,7 +2027,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1978,7 +2041,7 @@
         <v>75</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
@@ -1988,22 +2051,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{C24E788E-3061-4656-9920-E166B4DA38AF}"/>
+  <autoFilter ref="A1:G4" xr:uid="{7D836FA1-E7B9-4208-977A-E3DEFD2FF48A}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D905974D-916B-4B32-A6E6-1BB4A4CABC0B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5286005E-4F5E-4537-8B2C-408FFAAE933B}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -2037,7 +2100,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>76</v>
@@ -2060,7 +2123,7 @@
         <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>79</v>
@@ -2075,7 +2138,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -2089,7 +2152,7 @@
         <v>81</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>78</v>
@@ -2099,22 +2162,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{D905974D-916B-4B32-A6E6-1BB4A4CABC0B}"/>
+  <autoFilter ref="A1:G4" xr:uid="{5286005E-4F5E-4537-8B2C-408FFAAE933B}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D5552D-0EC2-4CEC-B1E7-7B39707D544F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D36E49F-0F76-437C-91A5-E9B6925B05CF}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -2256,22 +2319,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{35D5552D-0EC2-4CEC-B1E7-7B39707D544F}"/>
+  <autoFilter ref="A1:G6" xr:uid="{3D36E49F-0F76-437C-91A5-E9B6925B05CF}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9124780-6F4B-4428-8E4E-EF229C4CD882}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55DE5ACC-1B25-43EB-A5E2-1CD9612AB651}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -2320,7 +2383,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -2343,7 +2406,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -2351,16 +2414,16 @@
         <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>33</v>
@@ -2377,35 +2440,35 @@
         <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{C9124780-6F4B-4428-8E4E-EF229C4CD882}"/>
+  <autoFilter ref="A1:G5" xr:uid="{55DE5ACC-1B25-43EB-A5E2-1CD9612AB651}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B6F8FD-3D00-4EAF-9828-1CC2D13D61EC}">
-  <dimension ref="A1:G15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7746617C-53D1-4E0D-BD20-038CBD37074A}">
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="5" width="50.69921875" customWidth="1"/>
-    <col min="6" max="6" width="30.69921875" customWidth="1"/>
-    <col min="7" max="7" width="18.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -2439,16 +2502,16 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>33</v>
@@ -2462,16 +2525,16 @@
         <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>33</v>
@@ -2485,16 +2548,16 @@
         <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>33</v>
@@ -2508,22 +2571,22 @@
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="G5" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -2531,22 +2594,22 @@
         <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -2554,16 +2617,16 @@
         <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>105</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>33</v>
@@ -2577,16 +2640,16 @@
         <v>28</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>33</v>
@@ -2600,22 +2663,22 @@
         <v>28</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
@@ -2623,16 +2686,16 @@
         <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>33</v>
@@ -2640,45 +2703,45 @@
     </row>
     <row r="11" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>62</v>
+        <v>153</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>33</v>
@@ -2686,75 +2749,98 @@
     </row>
     <row r="13" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>62</v>
+        <v>156</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>62</v>
+        <v>160</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>62</v>
+        <v>164</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>33</v>
       </c>
     </row>
+    <row r="16" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G15" xr:uid="{95B6F8FD-3D00-4EAF-9828-1CC2D13D61EC}"/>
+  <autoFilter ref="A1:G16" xr:uid="{7746617C-53D1-4E0D-BD20-038CBD37074A}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/kintone-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/kintone-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2381E03E-A093-4F60-B9DD-6D6D93EBAA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3A0B1B8-3D82-4F5F-BB29-E9EF5F3020EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F679081C-2DE6-450E-92B4-A9DB47F8917A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CED0C3C0-900A-4D54-A195-988AB2A9C4CF}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -25,14 +25,14 @@
     <sheet name="2.9 環境設定（マスター）" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（一括実行）'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（一括実行）'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.2 実行（アプリデータ作成）'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2.3 実行（アプリデータ集計）'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2.4 実行（アラート集計）'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2.5 実行（投稿）'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 ログ'!$A$1:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 環境設定（共通）'!$A$1:$G$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'2.8 環境設定（グループ別）'!$A$1:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 環境設定（共通）'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'2.8 環境設定（グループ別）'!$A$1:$G$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（マスター）'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">一覧!$A$1:$C$10</definedName>
   </definedNames>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="349">
   <si>
     <t>通番</t>
   </si>
@@ -99,13 +99,16 @@
     <t>環境設定（共通）</t>
   </si>
   <si>
+    <t>32</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
     <t>環境設定（グループ別）</t>
   </si>
   <si>
-    <t>15</t>
+    <t>34</t>
   </si>
   <si>
     <t>9</t>
@@ -141,7 +144,8 @@
 アプリデータ作成-パルスサーベイ：あり
 アプリデータ集計-業務日誌・パルスサーベイ：あり
 アラート集計-業務日誌・パルスサーベイ：あり
-アラート集計-投稿：あり</t>
+アラート集計-投稿：あり
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象日」と「対象のグループ」を設定した後で、「実行」を押します。</t>
@@ -151,7 +155,11 @@
 状態（アプリデータ作成-パルスサーベイ）：成功または警告
 状態（アプリデータ集計-業務日誌・パルスサーベイ）：成功または警告
 状態（アラート集計-業務日誌・パルスサーベイ）：成功または警告
-状態（アラート集計-投稿）：成功または警告</t>
+状態（アラート集計-投稿）：成功または警告
+作成結果（業務日誌）：ok-業務日誌.txt
+作成結果（パルスサーベイ）：ok-パルスサーベイ.txt
+集計データ：ok-2026-09-01.txt
+アラート結果：ok.xlsx が作られる</t>
   </si>
   <si>
     <t>画面設計：3.1
@@ -167,7 +175,8 @@
 アプリデータ作成-パルスサーベイ：あり
 アプリデータ集計-業務日誌・パルスサーベイ：あり
 アラート集計-業務日誌・パルスサーベイ：あり
-アラート集計-投稿：あり</t>
+アラート集計-投稿：あり
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象日」と「対象のグループ」を設定した後で、「アプリデータ作成-業務日誌」のチェックを外して、「実行」を押します。</t>
@@ -180,17 +189,14 @@
 状態（アラート集計-投稿）：成功、警告、失敗のいずれか</t>
   </si>
   <si>
-    <t>「対象日」と「対象のグループ」を設定した後で、「実行」を押した後で、ログ欄を確認します。</t>
-  </si>
-  <si>
-    <t>ログ：一括実行 完了
-ログの出力先：logs フォルダがある</t>
-  </si>
-  <si>
     <t>「対象日」と「対象のグループ」を設定した後で、「実行」を押した後で、すべての行の「開く」を押します。</t>
   </si>
   <si>
-    <t>開いた画面：各処理の出力先のフォルダ、または対象のスレッド</t>
+    <t>開いた画面：開く（アプリデータ作成-業務日誌）：出力先のフォルダ
+開く（アプリデータ作成-パルスサーベイ）：出力先のフォルダ
+開く（アプリデータ集計-業務日誌・パルスサーベイ）：出力先のフォルダ
+開く（アラート集計-業務日誌・パルスサーベイ）：出力先のフォルダ
+開く（アラート集計-投稿）：対象のスレッド</t>
   </si>
   <si>
     <t>画面設計：3.1</t>
@@ -205,7 +211,8 @@
 アプリデータ作成-パルスサーベイ：あり
 アプリデータ集計-業務日誌・パルスサーベイ：あり
 アラート集計-業務日誌・パルスサーベイ：あり
-アラート集計-投稿：あり</t>
+アラート集計-投稿：あり
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>メッセージ：「対象日 を設定してください。」</t>
@@ -224,22 +231,24 @@
 アプリデータ作成-パルスサーベイ：あり
 アプリデータ集計-業務日誌・パルスサーベイ：あり
 アラート集計-業務日誌・パルスサーベイ：あり
-アラート集計-投稿：あり</t>
+アラート集計-投稿：あり
+設定ファイル：ng.bat</t>
   </si>
   <si>
     <t>状態（アプリデータ作成-業務日誌）：失敗
-後続の処理：実行される</t>
+状態（アプリデータ作成-パルスサーベイ）：成功、警告、失敗のいずれか</t>
   </si>
   <si>
     <t>対象日：2026-09-01
-対象のグループ：ok</t>
+対象のグループ：ok
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象日」と「対象のグループ」を設定した後で、「実行（業務日誌）」を押します。</t>
   </si>
   <si>
     <t>状態（業務日誌）：成功または警告
-集計用データ：作られる</t>
+集計用データ：ok-業務日誌.txt が作られる</t>
   </si>
   <si>
     <t>画面設計：3.2
@@ -259,7 +268,7 @@
   </si>
   <si>
     <t>状態（パルスサーベイ）：成功または警告
-集計用データ：作られる</t>
+集計用データ：ok-パルスサーベイ.txt が作られる</t>
   </si>
   <si>
     <t>画面設計：3.2
@@ -270,11 +279,13 @@
   </si>
   <si>
     <t>対象日：空
-対象のグループ：ok</t>
+対象のグループ：ok
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>対象日：2026-09-01
-対象のグループ：ng</t>
+対象のグループ：ng
+設定ファイル：ng.bat</t>
   </si>
   <si>
     <t>状態（業務日誌）：失敗</t>
@@ -283,18 +294,21 @@
     <t>状態（パルスサーベイ）：失敗</t>
   </si>
   <si>
-    <t>「実行（業務日誌）」と「実行（パルスサーベイ）」を順に実行し、「対象日」と「対象のグループ」を設定した後で、「実行」を押します。</t>
+    <t>対象日：2026-09-01
+対象のグループ：ok
+作成結果：ok-業務日誌.txt、ok-パルスサーベイ.txt
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>状態：成功または警告
-統合データ：作られる</t>
+統合データ：ok-2026-09-01.txt が作られる</t>
   </si>
   <si>
     <t>画面設計：3.3
 処理フロー：2.4</t>
   </si>
   <si>
-    <t>「実行（業務日誌）」と「実行（パルスサーベイ）」を順に実行し、「対象日」と「対象のグループ」を設定した後で、「実行」を押した後で、「開く」を押します。</t>
+    <t>「対象日」と「対象のグループ」を設定した後で、「実行」を押した後で、「開く」を押します。</t>
   </si>
   <si>
     <t>開いた画面：統合したデータのフォルダ</t>
@@ -303,18 +317,24 @@
     <t>画面設計：3.3</t>
   </si>
   <si>
-    <t>「実行（業務日誌）」と「実行（パルスサーベイ）」と「実行」を順に実行し、「対象日」と「対象のグループ」を設定した後で、「実行（業務日誌・パルスサーベイ）」を押します。</t>
+    <t>対象日：2026-09-01
+対象のグループ：ok
+集計データ：ok-2026-09-01.txt
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象日」と「対象のグループ」を設定した後で、「実行（業務日誌・パルスサーベイ）」を押します。</t>
   </si>
   <si>
     <t>状態（業務日誌・パルスサーベイ）：成功または警告
-アラート結果：作られる</t>
+アラート結果：ok.xlsx が作られる</t>
   </si>
   <si>
     <t>画面設計：3.4
 処理フロー：2.5</t>
   </si>
   <si>
-    <t>「実行（業務日誌）」と「実行（パルスサーベイ）」と「実行」を順に実行し、「対象日」と「対象のグループ」を設定した後で、「実行（業務日誌・パルスサーベイ）」を押した後で、「開く（業務日誌・パルスサーベイ）」を押します。</t>
+    <t>「対象日」と「対象のグループ」を設定した後で、「実行（業務日誌・パルスサーベイ）」を押した後で、「開く（業務日誌・パルスサーベイ）」を押します。</t>
   </si>
   <si>
     <t>開いた画面：検知結果のフォルダ</t>
@@ -323,41 +343,27 @@
     <t>画面設計：3.4</t>
   </si>
   <si>
-    <t>「対象日」と「対象のグループ」を設定した後で、「実行（業務日誌・パルスサーベイ）」を押します。</t>
-  </si>
-  <si>
-    <t>「実行（業務日誌）」と「実行（パルスサーベイ）」と「実行」と「実行（業務日誌・パルスサーベイ）」を順に実行し、「対象日」と「対象のグループ」を設定した後で、「実行（投稿）」を押します。</t>
-  </si>
-  <si>
-    <t>状態（投稿）：成功または警告
-投稿：投稿先のスレッドにコメントが投稿される</t>
+    <t>対象日：2026-09-01
+対象のグループ：ok
+アラート結果：ok-2026-09-01.xlsx
+集計テキスト：ok-2026-09-01.json
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象日」と「対象のグループ」を設定した後で、「実行（投稿）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（投稿）：成功または警告</t>
   </si>
   <si>
     <t>画面設計：3.4
 処理フロー：2.6</t>
   </si>
   <si>
-    <t>「実行（業務日誌）」と「実行（パルスサーベイ）」と「実行」と「実行（業務日誌・パルスサーベイ）」を順に実行し、「対象日」と「対象のグループ」を設定した後で、「実行（投稿）」を押した後で、「開く（投稿）」を押します。</t>
+    <t>「対象日」と「対象のグループ」を設定した後で、「実行（投稿）」を押した後で、「開く（投稿）」を押します。</t>
   </si>
   <si>
     <t>開いた画面：対象のスレッド（ブラウザ）</t>
-  </si>
-  <si>
-    <t>「対象日」と「対象のグループ」を設定した後で、「実行（投稿）」を押します。</t>
-  </si>
-  <si>
-    <t>対象のグループ：すべて
-処理：アプリデータ作成-業務日誌</t>
-  </si>
-  <si>
-    <t>ログのファイルがない状態で、「すべて削除」を押します。</t>
-  </si>
-  <si>
-    <t>メッセージ：「削除対象のログファイルがありません。」</t>
-  </si>
-  <si>
-    <t>画面設計：3.5
-処理フロー：2.7</t>
   </si>
   <si>
     <t>対象のグループ：すべて
@@ -365,10 +371,15 @@
 処理：アプリデータ作成-業務日誌</t>
   </si>
   <si>
-    <t>ログのファイルがある状態で、「すべて削除」を押し、確認で「いいえ」を押します。</t>
-  </si>
-  <si>
-    <t>ログのファイル：残る</t>
+    <t>「対象のグループ」を設定した後で、ログのファイルがある状態で、「すべて削除」を押し、確認で「いいえ」を押します。</t>
+  </si>
+  <si>
+    <t>確認ダイアログ：ログファイルを削除します
+ログ：残る</t>
+  </si>
+  <si>
+    <t>画面設計：3.5
+処理フロー：2.7</t>
   </si>
   <si>
     <t>対象のグループ：すべて
@@ -376,17 +387,18 @@
 処理：アプリデータ作成-業務日誌</t>
   </si>
   <si>
-    <t>ログのファイルがある状態で、「すべて削除」を押し、確認で「はい」を押します。</t>
-  </si>
-  <si>
-    <t>ログのファイル：すべて削除される</t>
+    <t>「対象のグループ」を設定した後で、ログのファイルがある状態で、「すべて削除」を押し、確認で「はい」を押します。</t>
+  </si>
+  <si>
+    <t>確認ダイアログ：ログファイルを削除します
+ログ：すべて削除される</t>
   </si>
   <si>
     <t>対象のグループ：すべて、ok
 処理：アプリデータ作成-業務日誌</t>
   </si>
   <si>
-    <t>「対象のグループ」を選びます。</t>
+    <t>「対象のグループ」を切り替えます。</t>
   </si>
   <si>
     <t>表示されるログ：「すべて」では ok と ng の両方、「ok」では ok のログだけ</t>
@@ -395,75 +407,486 @@
     <t>画面設計：3.5</t>
   </si>
   <si>
-    <t>対象のグループ：すべて、ok、ng、すべて
+    <t>対象のグループ：すべて
 処理：アプリデータ作成-業務日誌、アプリデータ作成-パルスサーベイ、アプリデータ集計-業務日誌・パルスサーベイ、アラート集計-業務日誌・パルスサーベイ、アラート集計-投稿、マスター同期</t>
   </si>
   <si>
-    <t>「アプリデータ作成-業務日誌」のラジオボタンを押し、「対象のグループ」を切り替えたあと、残りの処理のラジオボタンを上から順に切り替えます。</t>
+    <t>「対象のグループ」を設定した後で、「処理」のラジオボタンを「アプリデータ作成-業務日誌」、「アプリデータ作成-パルスサーベイ」、「アプリデータ集計-業務日誌・パルスサーベイ」、「アラート集計-業務日誌・パルスサーベイ」、「アラート集計-投稿」、「マスター同期」、「アプリデータ作成-業務日誌」の順に切り替えます。</t>
   </si>
   <si>
     <t>表示されるログ：選んだ処理のログだけ（ok と ng の両方）</t>
   </si>
   <si>
-    <t>基本設定：%BASE_PATH%clients_test</t>
+    <t>対象のグループ：すべて
+処理：アプリデータ作成-業務日誌</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、ログのファイルがない状態で、「すべて削除」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「削除対象のログファイルがありません。」</t>
+  </si>
+  <si>
+    <t>基本設定：saved-client-data
+設定ファイル：common.bat</t>
   </si>
   <si>
     <t>「基本設定」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：変えた値が保存される
-画面の表示：保存後の内容に更新</t>
+    <t>設定ファイル：common.bat の ClientDataRootDir が saved-client-data になる
+状態（保存）：完了</t>
   </si>
   <si>
     <t>画面設計：3.6
 処理フロー：2.8</t>
   </si>
   <si>
-    <t>基本設定：%BASE_PATH%clients_tmp</t>
+    <t>基本設定：tmp-reload
+設定ファイル：common.bat</t>
   </si>
   <si>
     <t>「基本設定」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>入力欄：保存されている値
-変えた内容：消える</t>
+    <t>基本設定：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
   </si>
   <si>
     <t>画面設計：3.6
 処理フロー：2.9</t>
   </si>
   <si>
-    <t>アプリデータ集計の列定義：13行目</t>
+    <t>グループデータのフォルダ：saved-client-data
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「グループデータのフォルダ」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に saved-client-data が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>グループデータのフォルダ：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「グループデータのフォルダ」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>グループデータのフォルダ：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>出力のルートフォルダ：saved-output-root
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「出力のルートフォルダ」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に saved-output-root が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>出力のルートフォルダ：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「出力のルートフォルダ」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>出力のルートフォルダ：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>テンプレートのフォルダ：saved-template
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「テンプレートのフォルダ」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に saved-template が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>テンプレートのフォルダ：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「テンプレートのフォルダ」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>テンプレートのフォルダ：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>ログの出力先：saved-log-path
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「ログの出力先」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に saved-log-path が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>ログの出力先：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「ログの出力先」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>ログの出力先：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>提出状況の出力先：saved-report-output
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「提出状況の出力先」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に saved-report-output が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>提出状況の出力先：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「提出状況の出力先」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>提出状況の出力先：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>アプリデータ集計の出力先：saved-collect-output
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「アプリデータ集計の出力先」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に saved-collect-output が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>アプリデータ集計の出力先：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「アプリデータ集計の出力先」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>アプリデータ集計の出力先：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>アラート検知結果の出力先：saved-alert-output
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「アラート検知結果の出力先」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に saved-alert-output が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>アラート検知結果の出力先：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「アラート検知結果の出力先」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>アラート検知結果の出力先：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>バックアップの出力先：saved-backup-output
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「バックアップの出力先」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に saved-backup-output が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>バックアップの出力先：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「バックアップの出力先」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>バックアップの出力先：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>業務日誌の日付フィールドコード：saved-daily-date
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「業務日誌の日付フィールドコード」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に saved-daily-date が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>業務日誌の日付フィールドコード：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「業務日誌の日付フィールドコード」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>業務日誌の日付フィールドコード：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>業務日誌の受講生IDフィールドコード：saved-daily-user
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「業務日誌の受講生IDフィールドコード」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に saved-daily-user が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>業務日誌の受講生IDフィールドコード：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「業務日誌の受講生IDフィールドコード」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>業務日誌の受講生IDフィールドコード：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>パルスサーベイの日付フィールドコード：saved-pulse-date
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「パルスサーベイの日付フィールドコード」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に saved-pulse-date が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>パルスサーベイの日付フィールドコード：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「パルスサーベイの日付フィールドコード」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>パルスサーベイの日付フィールドコード：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>パルスサーベイの受講生IDフィールドコード：saved-pulse-user
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「パルスサーベイの受講生IDフィールドコード」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に saved-pulse-user が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>パルスサーベイの受講生IDフィールドコード：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「パルスサーベイの受講生IDフィールドコード」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>パルスサーベイの受講生IDフィールドコード：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>アプリデータ集計の列定義：13行目
+列定義ファイル：collect-data-defs.json</t>
   </si>
   <si>
     <t>アプリデータ集計の列定義の13行目の「削除（アプリデータ集計の列定義）」を押します。</t>
   </si>
   <si>
-    <t>表：13行目の行が削除される</t>
+    <t>表：その行が削除される</t>
   </si>
   <si>
     <t>画面設計：3.6
 処理フロー：2.10</t>
   </si>
   <si>
-    <t>アプリデータ集計の列定義で、「追加（アプリデータ集計の列定義）」を押します。</t>
-  </si>
-  <si>
-    <t>表：末尾に空の行が追加される</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>列定義（14行目）変更前：saved-col
+設定ファイル：collect-data-defs.json</t>
+  </si>
+  <si>
+    <t>「追加（アプリデータ集計の列定義）」を押した後で、「変更前」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>表：末尾に行が追加される（未確認）、入力した値が collect-data-defs.json に保存される
+状態（保存）：完了</t>
   </si>
   <si>
     <t>画面設計：3.6
 処理フロー：2.11</t>
   </si>
   <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>列定義ファイル：collect-data-defs.json</t>
+  </si>
+  <si>
+    <t>アプリデータ集計の列定義の13行目の「削除（アプリデータ集計の列定義）」を押した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>状態（保存）：完了
+ファイル：collect-data-defs.json に、パルスサーベイフリーコメントの行が保存されない</t>
+  </si>
+  <si>
+    <t>画面設計：3.6
+処理フロー：2.8、2.10</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>列定義（13行目）の変更後：saved-col
+設定ファイル：collect-data-defs.json</t>
+  </si>
+  <si>
+    <t>「アプリデータ集計の列定義」の13行目の「変更後」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：collect-data-defs.json の newName が saved-col になる
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>列定義（13行目）の変更後：tmp-reload
+設定ファイル：collect-data-defs.json</t>
+  </si>
+  <si>
+    <t>「アプリデータ集計の列定義」の13行目の「変更後」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>列定義（13行目）の変更後：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>列定義（13行目）のタイプ：業務日誌
+設定ファイル：collect-data-defs.json</t>
+  </si>
+  <si>
+    <t>「アプリデータ集計の列定義」の13行目の「タイプ」を設定した後で、「保存」を押した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>列定義（13行目）のタイプ：（保存されている値）
+状態（保存）：完了
+状態（再読込）：完了</t>
+  </si>
+  <si>
     <t>対象のグループ：ok
-グループ名：ok（既存のグループ名）</t>
+設定ファイル：ok.bat
+グループ名：TestNew</t>
   </si>
   <si>
     <t>「対象のグループ」を設定した後で、「新規作成」を押し、「グループ名」を入力して「OK」を押します。</t>
   </si>
   <si>
-    <t>メッセージ：「（入力した名前）は既に存在します。」</t>
+    <t>一覧：名前が追加され、選ばれる</t>
   </si>
   <si>
     <t>画面設計：3.7
@@ -471,46 +894,62 @@
   </si>
   <si>
     <t>対象のグループ：ok
-グループ名：AggNew</t>
-  </si>
-  <si>
-    <t>一覧：名前が追加され、選ばれる</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-グループ名：AggUnsaved</t>
-  </si>
-  <si>
-    <t>「対象のグループ」を設定した後で、「新規作成」を押し、「グループ名」を入力して「OK」を押した後で、「コピー」を押します。</t>
-  </si>
-  <si>
-    <t>メッセージ：「コピー元のグループが存在しません。」</t>
+設定ファイル：ok.bat
+Excel ファイル：ok.xlsx
+グループ名：TestCopy</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「コピー」を押し、「グループ名」を入力して「OK」を押します。</t>
+  </si>
+  <si>
+    <t>一覧：TestCopy が選ばれる
+設定ファイル：TestCopy.bat が作られる
+Excel ファイル：TestCopy.xlsx が作られる</t>
   </si>
   <si>
     <t>画面設計：3.7
 処理フロー：2.13</t>
   </si>
   <si>
+    <t>対象のグループ：ok、入力なし（保存されている接続情報）
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「再読込」を押した後で、「テスト接続（認証情報）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（再読込）：完了
+状態（認証情報）：成功</t>
+  </si>
+  <si>
+    <t>画面設計：3.7
+処理フロー：2.16</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok、入力なし（保存されている投稿先）
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「テスト投稿」を押します。</t>
+  </si>
+  <si>
+    <t>状態（テスト投稿）：成功</t>
+  </si>
+  <si>
+    <t>画面設計：3.7
+処理フロー：2.20</t>
+  </si>
+  <si>
     <t>対象のグループ：ok
-グループ名：AggCopy</t>
-  </si>
-  <si>
-    <t>「対象のグループ」を設定した後で、「コピー」を押し、「グループ名」を入力して「OK」を押します。</t>
-  </si>
-  <si>
-    <t>一覧：AggCopy が選ばれる
-設定ファイル：AggCopy.bat が作られる
-Excel ファイル：AggCopy.xlsx が作られる</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-サブドメイン：saved</t>
+サブドメイン：saved-subdomain
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象のグループ」と「サブドメイン」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：値が保存される
+    <t>設定ファイル：ok.bat に saved-subdomain が保存される
+状態（保存）：完了
 画面の表示：保存後の内容に更新</t>
   </si>
   <si>
@@ -519,31 +958,202 @@
   </si>
   <si>
     <t>対象のグループ：ok
-サブドメイン：tmp</t>
+サブドメイン：tmp-reload
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象のグループ」と「サブドメイン」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>サブドメイン：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
   </si>
   <si>
     <t>画面設計：3.7
 処理フロー：2.15</t>
   </si>
   <si>
-    <t>対象のグループ：ok、入力なし（保存されている接続情報）</t>
-  </si>
-  <si>
-    <t>「対象のグループ」を設定した後で、「再読込」を押した後で、「テスト接続（認証情報）」を押します。</t>
-  </si>
-  <si>
-    <t>状態（認証情報）：成功</t>
-  </si>
-  <si>
-    <t>画面設計：3.7
-処理フロー：2.16</t>
-  </si>
-  <si>
     <t>対象のグループ：ok
-対象アプリID（業務日誌）：180</t>
+ログイン名：テスト用の値
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「ログイン名」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat の KintoneLoginName が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+ログイン名：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「ログイン名」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>ログイン名：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+パスワード：テスト用の値
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「パスワード」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat の KintonePassword が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+投稿先スペースID：saved-space-id
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「投稿先スペースID」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に saved-space-id が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+投稿先スペースID：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「投稿先スペースID」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>投稿先スペースID：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+投稿先スレッドID：saved-thread-id
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「投稿先スレッドID」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に saved-thread-id が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+投稿先スレッドID：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「投稿先スレッドID」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>投稿先スレッドID：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+投稿コメント文言：saved-comment
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「投稿コメント文言」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に saved-comment が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+投稿コメント文言：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「投稿コメント文言」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>投稿コメント文言：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+投稿集計文言：saved-summary
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「投稿集計文言」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に saved-summary が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+投稿集計文言：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「投稿集計文言」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>投稿集計文言：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+対象アプリID（ユーザー）：136
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「対象アプリID（ユーザー）」を設定した後で、「テスト接続（ユーザー）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（ユーザー）：成功</t>
+  </si>
+  <si>
+    <t>画面設計：3.8
+処理フロー：2.17</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+対象アプリID（ユーザー）：saved-user-app
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「対象アプリID（ユーザー）」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に saved-user-app が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+対象アプリID（ユーザー）：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「対象アプリID（ユーザー）」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>対象アプリID（ユーザー）：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+対象アプリID（業務日誌）：180
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象のグループ」と「対象アプリID（業務日誌）」を設定した後で、「テスト接続（業務日誌）」を押します。</t>
@@ -556,37 +1166,109 @@
 処理フロー：2.18</t>
   </si>
   <si>
-    <t>対象のグループ：ok、入力なし（保存されている投稿先）</t>
-  </si>
-  <si>
-    <t>「対象のグループ」を設定した後で、「テスト投稿」を押します。</t>
-  </si>
-  <si>
-    <t>状態（テスト投稿）：成功
-テスト用のコメント：投稿される</t>
-  </si>
-  <si>
-    <t>画面設計：3.7
-処理フロー：2.20</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok</t>
+    <t>対象のグループ：ok
+対象アプリID（業務日誌）：saved-daily-app
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「対象アプリID（業務日誌）」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に saved-daily-app が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+対象アプリID（業務日誌）：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「対象アプリID（業務日誌）」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>対象アプリID（業務日誌）：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+対象アプリID（パルスサーベイ）：181
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「対象アプリID（パルスサーベイ）」を設定した後で、「テスト接続（パルスサーベイ）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（パルスサーベイ）：成功</t>
+  </si>
+  <si>
+    <t>画面設計：3.8
+処理フロー：2.19</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+対象アプリID（パルスサーベイ）：saved-pulse-app
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「対象アプリID（パルスサーベイ）」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat に saved-pulse-app が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+対象アプリID（パルスサーベイ）：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「対象アプリID（パルスサーベイ）」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>対象アプリID（パルスサーベイ）：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat
+グループ名：ok（既存のグループ名）</t>
+  </si>
+  <si>
+    <t>メッセージ：「（入力した名前）は既に存在します。」</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat
+グループ名：TestUnsaved</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「新規作成」を押し、「グループ名」を入力して「OK」を押した後で、「コピー」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「コピー元のグループが存在しません。」</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象のグループ」を設定した後で、「新規作成」を押した後で、「キャンセル」を押します。</t>
   </si>
   <si>
-    <t>ダイアログが閉じる</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>ファイル：TestCancel.bat が作られない</t>
   </si>
   <si>
     <t>対象のグループ：ok
-サブドメイン：空</t>
+設定ファイル：ok.bat
+Excel ファイル：ok.xlsx
+グループ名：ok（既存のグループ名）</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+サブドメイン：空
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象のグループ」と「サブドメイン」を設定した後で、「テスト接続（認証情報）」を押します。</t>
@@ -596,52 +1278,57 @@
 状態（認証情報）：失敗</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>対象のグループ：ok
-対象アプリID（業務日誌）：空</t>
+パスワード：誤った値
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「パスワード」を設定した後で、「テスト接続（認証情報）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（認証情報）：失敗</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+投稿先スペースID：空
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「投稿先スペースID」を設定した後で、「テスト投稿」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「エラーが発生しました: スペースID／スレッドIDを入力してください。」
+状態（テスト投稿）：失敗</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+対象アプリID（業務日誌）：空
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>メッセージ：「エラーが発生しました: 対象アプリIDを入力してください。」
 状態（業務日誌）：失敗</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-投稿先スペースID：空</t>
-  </si>
-  <si>
-    <t>「対象のグループ」と「投稿先スペースID」を設定した後で、「テスト投稿」を押します。</t>
-  </si>
-  <si>
-    <t>メッセージ：「エラーが発生しました: スペースID／スレッドIDを入力してください。」
-状態（テスト投稿）：失敗</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-パスワード：wrong-password</t>
-  </si>
-  <si>
-    <t>「対象のグループ」と「パスワード」を設定した後で、「テスト接続（認証情報）」を押します。</t>
-  </si>
-  <si>
-    <t>状態（認証情報）：失敗</t>
-  </si>
-  <si>
-    <t>メッセージ：「（入力した名前）は既に存在します。」
-一覧：追加されない</t>
-  </si>
-  <si>
-    <t>「対象のグループ」を設定した後で、スケジュールの1行目の「削除（スケジュール）」を押します。</t>
-  </si>
-  <si>
-    <t>表：選んだ行が削除される</t>
+    <t>「対象のグループ」を設定した後で、「同期実行」を押します。</t>
+  </si>
+  <si>
+    <t>状態（同期実行）：成功</t>
+  </si>
+  <si>
+    <t>画面設計：3.8
+処理フロー：2.23</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、スケジュールの1行目の「削除（スケジュール）」を押した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>表：その行が削除される
+状態（保存）：完了
+ファイル：ok.xlsx のスケジュールの科目名（1行目）が空になる</t>
   </si>
   <si>
     <t>画面設計：3.8
@@ -649,13 +1336,16 @@
   </si>
   <si>
     <t>対象のグループ：ok
-科目名：テスト科目</t>
+科目名：saved-subject
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象のグループ」を設定し、スケジュールの1行目の「科目名」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>画面の表示：保存後の内容（テスト科目）が表示される</t>
+    <t>画面の表示：保存後の内容（saved-subject）が表示される
+状態（保存）：完了
+ファイル：ok.xlsx のスケジュールの科目名（1行目）が saved-subject になる</t>
   </si>
   <si>
     <t>画面設計：3.8
@@ -663,38 +1353,34 @@
   </si>
   <si>
     <t>対象のグループ：ok
-科目名：一時</t>
+科目名：tmp-reload
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象のグループ」を設定し、スケジュールの1行目の「科目名」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
-    <t>表：保存されている値で表示し直される
-変えた内容：消える</t>
+    <t>スケジュールの科目名（1行目）：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
   </si>
   <si>
     <t>画面設計：3.8
 処理フロー：2.22</t>
   </si>
   <si>
-    <t>「対象のグループ」を設定した後で、「同期実行」を押します。</t>
-  </si>
-  <si>
-    <t>状態（同期実行）：成功</t>
-  </si>
-  <si>
-    <t>画面設計：3.8
-処理フロー：2.23</t>
-  </si>
-  <si>
     <t>「対象のグループ」を設定した後で、「追加（スケジュール）」を押します。</t>
+  </si>
+  <si>
+    <t>表：末尾に2行目が追加される（未確認）、通番は2になる</t>
   </si>
   <si>
     <t>画面設計：3.8
 処理フロー：2.25</t>
   </si>
   <si>
-    <t>対象のグループ：ng</t>
+    <t>対象のグループ：ng
+設定ファイル：ng.bat</t>
   </si>
   <si>
     <t>状態（同期実行）：失敗</t>
@@ -702,7 +1388,7 @@
   <si>
     <t>メッセージ：「エラーが発生しました: 対象アプリIDが設定されていません。」
 状態（同期実行）：失敗
-ユーザーマスター：書き込まれない</t>
+ユーザーマスター：書き込まれない（未確認）</t>
   </si>
 </sst>
 </file>
@@ -1101,7 +1787,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86ACF708-E795-405D-82D8-9F96DF75AE8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D13F1AA6-78D8-4A35-AF7B-E1B466F868FD}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1194,40 +1880,40 @@
         <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="54" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="54" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10" xr:uid="{86ACF708-E795-405D-82D8-9F96DF75AE8D}"/>
+  <autoFilter ref="A1:C10" xr:uid="{D13F1AA6-78D8-4A35-AF7B-E1B466F868FD}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8A28B49-29AC-4AF0-8235-9256E856B8B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDD42771-5A66-402B-B525-7CCD15DA44B9}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1243,114 +1929,114 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>147</v>
+        <v>313</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>166</v>
+        <v>329</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>167</v>
+        <v>330</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>168</v>
+        <v>331</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>169</v>
+        <v>313</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>170</v>
+        <v>332</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>171</v>
+        <v>333</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>172</v>
+        <v>334</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="378" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>173</v>
+        <v>335</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>174</v>
+        <v>336</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>175</v>
+        <v>337</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>176</v>
+        <v>338</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>147</v>
+        <v>339</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>177</v>
+        <v>340</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>178</v>
+        <v>341</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>179</v>
+        <v>342</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="180" x14ac:dyDescent="0.45">
@@ -1358,22 +2044,22 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>147</v>
+        <v>313</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>180</v>
+        <v>343</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>112</v>
+        <v>344</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>181</v>
+        <v>345</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="144" x14ac:dyDescent="0.45">
@@ -1381,56 +2067,236 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>182</v>
+        <v>346</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>177</v>
+        <v>329</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>183</v>
+        <v>347</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>179</v>
+        <v>331</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="324" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="342" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>182</v>
+        <v>346</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>177</v>
+        <v>329</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>184</v>
+        <v>348</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>179</v>
+        <v>331</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{D8A28B49-29AC-4AF0-8235-9256E856B8B9}"/>
+  <autoFilter ref="A1:G8" xr:uid="{BDD42771-5A66-402B-B525-7CCD15DA44B9}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95DCF242-8AC0-40DF-B6A5-B0611851AEEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9629AE74-7231-4EAB-9479-F4C57DB62C10}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G7" xr:uid="{9629AE74-7231-4EAB-9479-F4C57DB62C10}"/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9599AC6B-5042-4052-8434-71650D5CC6D0}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1446,225 +2312,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{95DCF242-8AC0-40DF-B6A5-B0611851AEEB}"/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF3AF382-18C0-4D94-8D1B-661362719FCC}">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="5" width="70.69921875" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" customWidth="1"/>
-    <col min="7" max="7" width="12.69921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -1672,22 +2335,22 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="288" x14ac:dyDescent="0.45">
@@ -1695,22 +2358,22 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -1718,22 +2381,22 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="306" x14ac:dyDescent="0.45">
@@ -1741,22 +2404,22 @@
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -1764,22 +2427,22 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -1787,22 +2450,22 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -1810,33 +2473,33 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{DF3AF382-18C0-4D94-8D1B-661362719FCC}"/>
+  <autoFilter ref="A1:G8" xr:uid="{9599AC6B-5042-4052-8434-71650D5CC6D0}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B185A71B-3A5C-4B56-9651-50BDD14AE1C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E2D3B8-B3CE-406A-A61B-FAD0AC248A76}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1852,68 +2515,68 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="306" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="360" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
@@ -1921,33 +2584,33 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{B185A71B-3A5C-4B56-9651-50BDD14AE1C0}"/>
+  <autoFilter ref="A1:G4" xr:uid="{38E2D3B8-B3CE-406A-A61B-FAD0AC248A76}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D836FA1-E7B9-4208-977A-E3DEFD2FF48A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D28BA69-3E39-435C-B67A-DB543C59C27F}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1963,33 +2626,33 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>69</v>
@@ -2001,18 +2664,18 @@
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="360" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>72</v>
@@ -2024,7 +2687,7 @@
         <v>74</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -2032,33 +2695,33 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{7D836FA1-E7B9-4208-977A-E3DEFD2FF48A}"/>
+  <autoFilter ref="A1:G4" xr:uid="{9D28BA69-3E39-435C-B67A-DB543C59C27F}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5286005E-4F5E-4537-8B2C-408FFAAE933B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68878104-4BB9-41E5-A5E2-28DC52AC353B}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2074,33 +2737,33 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="342" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>76</v>
@@ -2112,18 +2775,18 @@
         <v>78</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="342" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>79</v>
@@ -2135,7 +2798,7 @@
         <v>74</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -2143,33 +2806,33 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{5286005E-4F5E-4537-8B2C-408FFAAE933B}"/>
+  <autoFilter ref="A1:G4" xr:uid="{68878104-4BB9-41E5-A5E2-28DC52AC353B}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D36E49F-0F76-437C-91A5-E9B6925B05CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE17FC8-0FFB-43B9-B88D-408E8F7383E5}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2185,99 +2848,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>92</v>
@@ -2289,45 +2952,45 @@
         <v>94</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{3D36E49F-0F76-437C-91A5-E9B6925B05CF}"/>
+  <autoFilter ref="A1:G6" xr:uid="{ACE17FC8-0FFB-43B9-B88D-408E8F7383E5}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55DE5ACC-1B25-43EB-A5E2-1CD9612AB651}">
-  <dimension ref="A1:G5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCCEF974-4D11-4351-A690-9B318A968D12}">
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
@@ -2342,68 +3005,68 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -2411,57 +3074,701 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>33</v>
+      <c r="E6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A24" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A25" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A26" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A27" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A28" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A29" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A30" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A31" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A32" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A33" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{55DE5ACC-1B25-43EB-A5E2-1CD9612AB651}"/>
+  <autoFilter ref="A1:G33" xr:uid="{DCCEF974-4D11-4351-A690-9B318A968D12}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7746617C-53D1-4E0D-BD20-038CBD37074A}">
-  <dimension ref="A1:G16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82428735-F36E-4909-9AD5-47F1C98B3656}">
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
@@ -2476,22 +3783,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -2499,348 +3806,785 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>114</v>
+        <v>221</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>115</v>
+        <v>222</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>116</v>
+        <v>223</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>117</v>
+        <v>224</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>118</v>
+        <v>225</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>115</v>
+        <v>226</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>119</v>
+        <v>227</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>117</v>
+        <v>228</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>120</v>
+        <v>229</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>121</v>
+        <v>230</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>122</v>
+        <v>231</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>123</v>
+        <v>232</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>124</v>
+        <v>233</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>125</v>
+        <v>234</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>126</v>
+        <v>235</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>123</v>
+        <v>236</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>127</v>
+        <v>237</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>128</v>
+        <v>238</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>129</v>
+        <v>239</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>131</v>
+        <v>241</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>132</v>
+        <v>242</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>105</v>
+        <v>243</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>134</v>
+        <v>245</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="270" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A24" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+      <c r="A25" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A26" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A27" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A28" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+      <c r="A29" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A30" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A31" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="306" x14ac:dyDescent="0.45">
+      <c r="A32" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A33" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="144" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
+      <c r="B33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A34" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A35" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="216" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="306" x14ac:dyDescent="0.45">
-      <c r="A12" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="270" x14ac:dyDescent="0.45">
-      <c r="A13" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="270" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="234" x14ac:dyDescent="0.45">
-      <c r="A15" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="234" x14ac:dyDescent="0.45">
-      <c r="A16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>33</v>
+      <c r="B35" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G16" xr:uid="{7746617C-53D1-4E0D-BD20-038CBD37074A}"/>
+  <autoFilter ref="A1:G35" xr:uid="{82428735-F36E-4909-9AD5-47F1C98B3656}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/kintone-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/kintone-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3A0B1B8-3D82-4F5F-BB29-E9EF5F3020EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51129893-D3B7-4F12-8029-DCC295E182A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CED0C3C0-900A-4D54-A195-988AB2A9C4CF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2FEFC4D8-1CEF-4EBD-9C6C-E1B71B5C6001}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <sheet name="2.9 環境設定（マスター）" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（一括実行）'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（一括実行）'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.2 実行（アプリデータ作成）'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2.3 実行（アプリデータ集計）'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2.4 実行（アラート集計）'!$A$1:$G$4</definedName>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="345">
   <si>
     <t>通番</t>
   </si>
@@ -63,15 +63,18 @@
     <t>実行（一括実行）</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>実行（アプリデータ作成）</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>実行（アプリデータ作成）</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -82,9 +85,6 @@
   </si>
   <si>
     <t>実行（アラート集計）</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
   <si>
     <t>実行（投稿）</t>
@@ -151,15 +151,16 @@
     <t>「対象日」と「対象のグループ」を設定した後で、「実行」を押します。</t>
   </si>
   <si>
-    <t>状態（アプリデータ作成-業務日誌）：成功または警告
-状態（アプリデータ作成-パルスサーベイ）：成功または警告
-状態（アプリデータ集計-業務日誌・パルスサーベイ）：成功または警告
-状態（アラート集計-業務日誌・パルスサーベイ）：成功または警告
-状態（アラート集計-投稿）：成功または警告
-作成結果（業務日誌）：ok-業務日誌.txt
-作成結果（パルスサーベイ）：ok-パルスサーベイ.txt
-集計データ：ok-2026-09-01.txt
-アラート結果：ok.xlsx が作られる</t>
+    <t>状態（アプリデータ作成-業務日誌）：成功
+状態（アプリデータ作成-パルスサーベイ）：成功
+状態（アプリデータ集計-業務日誌・パルスサーベイ）：成功
+状態（アラート集計-業務日誌・パルスサーベイ）：成功
+状態（アラート集計-投稿）：成功
+状態：成功
+集計用データ（業務日誌）：ok-業務日誌.txt
+集計用データ（パルスサーベイ）：ok-パルスサーベイ.txt
+統合データ：ok-2026-09-01.txt
+アラート結果：ok.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.1
@@ -171,28 +172,29 @@
   <si>
     <t>対象日：2026-09-01
 対象のグループ：ok
-アプリデータ作成-業務日誌：なし
+アプリデータ作成-業務日誌：あり
 アプリデータ作成-パルスサーベイ：あり
 アプリデータ集計-業務日誌・パルスサーベイ：あり
 アラート集計-業務日誌・パルスサーベイ：あり
-アラート集計-投稿：あり
+アラート集計-投稿：なし
 設定ファイル：ok.bat</t>
   </si>
   <si>
-    <t>「対象日」と「対象のグループ」を設定した後で、「アプリデータ作成-業務日誌」のチェックを外して、「実行」を押します。</t>
-  </si>
-  <si>
-    <t>状態（アプリデータ作成-業務日誌）：スキップ
-状態（アプリデータ作成-パルスサーベイ）：成功、警告、失敗のいずれか
-状態（アプリデータ集計-業務日誌・パルスサーベイ）：成功、警告、失敗のいずれか
-状態（アラート集計-業務日誌・パルスサーベイ）：成功、警告、失敗のいずれか
-状態（アラート集計-投稿）：成功、警告、失敗のいずれか</t>
+    <t>「対象日」と「対象のグループ」を設定した後で、「アラート集計-投稿」のチェックを外して、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>状態（アプリデータ作成-業務日誌）：成功
+状態（アプリデータ作成-パルスサーベイ）：成功
+状態（アプリデータ集計-業務日誌・パルスサーベイ）：成功
+状態（アラート集計-業務日誌・パルスサーベイ）：成功
+状態（アラート集計-投稿）：スキップ
+状態：成功</t>
   </si>
   <si>
     <t>「対象日」と「対象のグループ」を設定した後で、「実行」を押した後で、すべての行の「開く」を押します。</t>
   </si>
   <si>
-    <t>開いた画面：開く（アプリデータ作成-業務日誌）：出力先のフォルダ
+    <t>開く（アプリデータ作成-業務日誌）：出力先のフォルダ
 開く（アプリデータ作成-パルスサーベイ）：出力先のフォルダ
 開く（アプリデータ集計-業務日誌・パルスサーベイ）：出力先のフォルダ
 開く（アラート集計-業務日誌・パルスサーベイ）：出力先のフォルダ
@@ -218,13 +220,6 @@
     <t>メッセージ：「対象日 を設定してください。」</t>
   </si>
   <si>
-    <t>状態（アプリデータ作成-業務日誌）：成功、警告、失敗、スキップのいずれか
-状態（アプリデータ作成-パルスサーベイ）：成功、警告、失敗、スキップのいずれか
-状態（アプリデータ集計-業務日誌・パルスサーベイ）：成功、警告、失敗、スキップのいずれか
-状態（アラート集計-業務日誌・パルスサーベイ）：成功、警告、失敗、スキップのいずれか
-状態（アラート集計-投稿）：成功、警告、失敗、スキップのいずれか</t>
-  </si>
-  <si>
     <t>対象日：2026-09-01
 対象のグループ：ng
 アプリデータ作成-業務日誌：あり
@@ -236,7 +231,11 @@
   </si>
   <si>
     <t>状態（アプリデータ作成-業務日誌）：失敗
-状態（アプリデータ作成-パルスサーベイ）：成功、警告、失敗のいずれか</t>
+状態（アプリデータ作成-パルスサーベイ）：失敗
+状態（アプリデータ集計-業務日誌・パルスサーベイ）：失敗
+状態（アラート集計-業務日誌・パルスサーベイ）：成功
+状態（アラート集計-投稿）：失敗
+状態：失敗</t>
   </si>
   <si>
     <t>対象日：2026-09-01
@@ -247,8 +246,8 @@
     <t>「対象日」と「対象のグループ」を設定した後で、「実行（業務日誌）」を押します。</t>
   </si>
   <si>
-    <t>状態（業務日誌）：成功または警告
-集計用データ：ok-業務日誌.txt が作られる</t>
+    <t>状態（業務日誌）：成功
+集計用データ：ok-業務日誌.txt</t>
   </si>
   <si>
     <t>画面設計：3.2
@@ -258,7 +257,7 @@
     <t>「対象日」と「対象のグループ」を設定した後で、「実行（業務日誌）」を押した後で、「開く（業務日誌）」を押します。</t>
   </si>
   <si>
-    <t>開いた画面：作成したデータのフォルダ</t>
+    <t>開く：出力先のフォルダ</t>
   </si>
   <si>
     <t>画面設計：3.2</t>
@@ -267,8 +266,8 @@
     <t>「対象日」と「対象のグループ」を設定した後で、「実行（パルスサーベイ）」を押します。</t>
   </si>
   <si>
-    <t>状態（パルスサーベイ）：成功または警告
-集計用データ：ok-パルスサーベイ.txt が作られる</t>
+    <t>状態（パルスサーベイ）：成功
+集計用データ：ok-パルスサーベイ.txt</t>
   </si>
   <si>
     <t>画面設計：3.2
@@ -300,8 +299,8 @@
 設定ファイル：ok.bat</t>
   </si>
   <si>
-    <t>状態：成功または警告
-統合データ：ok-2026-09-01.txt が作られる</t>
+    <t>状態：成功
+統合データ：ok-2026-09-01.txt</t>
   </si>
   <si>
     <t>画面設計：3.3
@@ -309,9 +308,6 @@
   </si>
   <si>
     <t>「対象日」と「対象のグループ」を設定した後で、「実行」を押した後で、「開く」を押します。</t>
-  </si>
-  <si>
-    <t>開いた画面：統合したデータのフォルダ</t>
   </si>
   <si>
     <t>画面設計：3.3</t>
@@ -326,8 +322,8 @@
     <t>「対象日」と「対象のグループ」を設定した後で、「実行（業務日誌・パルスサーベイ）」を押します。</t>
   </si>
   <si>
-    <t>状態（業務日誌・パルスサーベイ）：成功または警告
-アラート結果：ok.xlsx が作られる</t>
+    <t>状態（業務日誌・パルスサーベイ）：成功
+アラート結果：ok.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.4
@@ -335,9 +331,6 @@
   </si>
   <si>
     <t>「対象日」と「対象のグループ」を設定した後で、「実行（業務日誌・パルスサーベイ）」を押した後で、「開く（業務日誌・パルスサーベイ）」を押します。</t>
-  </si>
-  <si>
-    <t>開いた画面：検知結果のフォルダ</t>
   </si>
   <si>
     <t>画面設計：3.4</t>
@@ -353,7 +346,7 @@
     <t>「対象日」と「対象のグループ」を設定した後で、「実行（投稿）」を押します。</t>
   </si>
   <si>
-    <t>状態（投稿）：成功または警告</t>
+    <t>状態（投稿）：成功</t>
   </si>
   <si>
     <t>画面設計：3.4
@@ -363,7 +356,7 @@
     <t>「対象日」と「対象のグループ」を設定した後で、「実行（投稿）」を押した後で、「開く（投稿）」を押します。</t>
   </si>
   <si>
-    <t>開いた画面：対象のスレッド（ブラウザ）</t>
+    <t>開く：対象のスレッド</t>
   </si>
   <si>
     <t>対象のグループ：すべて
@@ -434,7 +427,7 @@
     <t>「基本設定」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat の ClientDataRootDir が saved-client-data になる
+    <t>設定ファイル：common.bat に saved-client-data が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -463,10 +456,6 @@
   </si>
   <si>
     <t>「グループデータのフォルダ」を設定した後で、「保存」を押します。</t>
-  </si>
-  <si>
-    <t>設定ファイル：common.bat に saved-client-data が保存される
-状態（保存）：完了</t>
   </si>
   <si>
     <t>グループデータのフォルダ：tmp-reload
@@ -903,8 +892,8 @@
   </si>
   <si>
     <t>一覧：TestCopy が選ばれる
-設定ファイル：TestCopy.bat が作られる
-Excel ファイル：TestCopy.xlsx が作られる</t>
+設定ファイル：TestCopy.bat
+Excel ファイル：TestCopy.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.7
@@ -949,8 +938,7 @@
   </si>
   <si>
     <t>設定ファイル：ok.bat に saved-subdomain が保存される
-状態（保存）：完了
-画面の表示：保存後の内容に更新</t>
+状態（保存）：完了</t>
   </si>
   <si>
     <t>画面設計：3.7
@@ -1787,7 +1775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D13F1AA6-78D8-4A35-AF7B-E1B466F868FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{501550C8-109F-40F0-9CCC-621C7510CA66}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1825,40 +1813,40 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="54" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="54" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="36" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
@@ -1869,12 +1857,12 @@
         <v>15</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="36" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1902,18 +1890,18 @@
         <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10" xr:uid="{D13F1AA6-78D8-4A35-AF7B-E1B466F868FD}"/>
+  <autoFilter ref="A1:C10" xr:uid="{501550C8-109F-40F0-9CCC-621C7510CA66}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDD42771-5A66-402B-B525-7CCD15DA44B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A1A3EA-EA03-4CB9-ADE0-1DF818399A72}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1955,16 +1943,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -1978,16 +1966,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -1995,22 +1983,22 @@
     </row>
     <row r="4" spans="1:7" ht="378" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -2018,22 +2006,22 @@
     </row>
     <row r="5" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -2041,22 +2029,22 @@
     </row>
     <row r="6" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -2070,16 +2058,16 @@
         <v>41</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -2087,37 +2075,37 @@
     </row>
     <row r="8" spans="1:7" ht="342" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{BDD42771-5A66-402B-B525-7CCD15DA44B9}"/>
+  <autoFilter ref="A1:G8" xr:uid="{86A1A3EA-EA03-4CB9-ADE0-1DF818399A72}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9629AE74-7231-4EAB-9479-F4C57DB62C10}">
-  <dimension ref="A1:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9633EDDE-2439-4D54-8946-C6EAF7CD4194}">
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
@@ -2198,7 +2186,7 @@
     </row>
     <row r="4" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>29</v>
@@ -2221,7 +2209,7 @@
     </row>
     <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>41</v>
@@ -2244,19 +2232,19 @@
     </row>
     <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>33</v>
@@ -2265,38 +2253,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{9629AE74-7231-4EAB-9479-F4C57DB62C10}"/>
+  <autoFilter ref="A1:G6" xr:uid="{9633EDDE-2439-4D54-8946-C6EAF7CD4194}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9599AC6B-5042-4052-8434-71650D5CC6D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BCD030D-3EFA-476E-9D6D-D3F11CD0E0CC}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2338,16 +2303,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -2361,16 +2326,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -2378,22 +2343,22 @@
     </row>
     <row r="4" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -2401,22 +2366,22 @@
     </row>
     <row r="5" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -2424,22 +2389,22 @@
     </row>
     <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>43</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -2453,16 +2418,16 @@
         <v>41</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -2470,36 +2435,36 @@
     </row>
     <row r="8" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{9599AC6B-5042-4052-8434-71650D5CC6D0}"/>
+  <autoFilter ref="A1:G8" xr:uid="{1BCD030D-3EFA-476E-9D6D-D3F11CD0E0CC}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E2D3B8-B3CE-406A-A61B-FAD0AC248A76}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{962D8032-8D9E-46CD-AF9C-8ABFE96F93A5}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2541,16 +2506,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -2564,16 +2529,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -2581,13 +2546,13 @@
     </row>
     <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>31</v>
@@ -2596,21 +2561,21 @@
         <v>43</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{38E2D3B8-B3CE-406A-A61B-FAD0AC248A76}"/>
+  <autoFilter ref="A1:G4" xr:uid="{962D8032-8D9E-46CD-AF9C-8ABFE96F93A5}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D28BA69-3E39-435C-B67A-DB543C59C27F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB9CBED-7A27-42BB-B63F-79191EE2E815}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2652,16 +2617,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -2675,16 +2640,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -2692,36 +2657,36 @@
     </row>
     <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>43</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{9D28BA69-3E39-435C-B67A-DB543C59C27F}"/>
+  <autoFilter ref="A1:G4" xr:uid="{2AB9CBED-7A27-42BB-B63F-79191EE2E815}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68878104-4BB9-41E5-A5E2-28DC52AC353B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F17C32A5-93A6-4873-8A5C-1FAAD49C80FE}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2763,16 +2728,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -2786,16 +2751,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -2803,36 +2768,36 @@
     </row>
     <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>43</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{68878104-4BB9-41E5-A5E2-28DC52AC353B}"/>
+  <autoFilter ref="A1:G4" xr:uid="{F17C32A5-93A6-4873-8A5C-1FAAD49C80FE}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE17FC8-0FFB-43B9-B88D-408E8F7383E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD14226C-85DF-4D3E-9BD3-13A6D76D0250}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2874,16 +2839,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -2897,16 +2862,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -2914,22 +2879,22 @@
     </row>
     <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -2937,22 +2902,22 @@
     </row>
     <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -2960,36 +2925,36 @@
     </row>
     <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{ACE17FC8-0FFB-43B9-B88D-408E8F7383E5}"/>
+  <autoFilter ref="A1:G6" xr:uid="{CD14226C-85DF-4D3E-9BD3-13A6D76D0250}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCCEF974-4D11-4351-A690-9B318A968D12}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB437315-07BF-446C-9160-D5C8C02E30B4}">
   <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3023,7 +2988,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -3031,16 +2996,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -3054,16 +3019,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -3071,22 +3036,22 @@
     </row>
     <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -3094,22 +3059,22 @@
     </row>
     <row r="5" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -3117,22 +3082,22 @@
     </row>
     <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -3146,16 +3111,16 @@
         <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -3163,22 +3128,22 @@
     </row>
     <row r="8" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
@@ -3192,16 +3157,16 @@
         <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
@@ -3215,16 +3180,16 @@
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
@@ -3232,22 +3197,22 @@
     </row>
     <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
@@ -3255,22 +3220,22 @@
     </row>
     <row r="12" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>34</v>
@@ -3278,22 +3243,22 @@
     </row>
     <row r="13" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>34</v>
@@ -3301,22 +3266,22 @@
     </row>
     <row r="14" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>34</v>
@@ -3324,22 +3289,22 @@
     </row>
     <row r="15" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>34</v>
@@ -3347,22 +3312,22 @@
     </row>
     <row r="16" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>34</v>
@@ -3370,22 +3335,22 @@
     </row>
     <row r="17" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>34</v>
@@ -3393,22 +3358,22 @@
     </row>
     <row r="18" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>34</v>
@@ -3416,22 +3381,22 @@
     </row>
     <row r="19" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>34</v>
@@ -3439,22 +3404,22 @@
     </row>
     <row r="20" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>34</v>
@@ -3462,22 +3427,22 @@
     </row>
     <row r="21" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>34</v>
@@ -3485,22 +3450,22 @@
     </row>
     <row r="22" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>34</v>
@@ -3508,22 +3473,22 @@
     </row>
     <row r="23" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>34</v>
@@ -3531,22 +3496,22 @@
     </row>
     <row r="24" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>34</v>
@@ -3554,22 +3519,22 @@
     </row>
     <row r="25" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>34</v>
@@ -3577,22 +3542,22 @@
     </row>
     <row r="26" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>34</v>
@@ -3600,22 +3565,22 @@
     </row>
     <row r="27" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>34</v>
@@ -3623,22 +3588,22 @@
     </row>
     <row r="28" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>34</v>
@@ -3646,22 +3611,22 @@
     </row>
     <row r="29" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>34</v>
@@ -3669,22 +3634,22 @@
     </row>
     <row r="30" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>34</v>
@@ -3692,22 +3657,22 @@
     </row>
     <row r="31" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>34</v>
@@ -3715,22 +3680,22 @@
     </row>
     <row r="32" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>34</v>
@@ -3744,30 +3709,30 @@
         <v>29</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G33" xr:uid="{DCCEF974-4D11-4351-A690-9B318A968D12}"/>
+  <autoFilter ref="A1:G33" xr:uid="{AB437315-07BF-446C-9160-D5C8C02E30B4}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82428735-F36E-4909-9AD5-47F1C98B3656}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD8E7D05-249C-4E1C-844F-D4D296C174CB}">
   <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3809,22 +3774,22 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -3832,16 +3797,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -3849,22 +3814,22 @@
     </row>
     <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -3872,45 +3837,45 @@
     </row>
     <row r="5" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="252" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -3924,16 +3889,16 @@
         <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -3941,22 +3906,22 @@
     </row>
     <row r="8" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
@@ -3970,16 +3935,16 @@
         <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
@@ -3993,16 +3958,16 @@
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
@@ -4010,22 +3975,22 @@
     </row>
     <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
@@ -4033,22 +3998,22 @@
     </row>
     <row r="12" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>34</v>
@@ -4056,22 +4021,22 @@
     </row>
     <row r="13" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>34</v>
@@ -4079,22 +4044,22 @@
     </row>
     <row r="14" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>34</v>
@@ -4102,22 +4067,22 @@
     </row>
     <row r="15" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>34</v>
@@ -4125,22 +4090,22 @@
     </row>
     <row r="16" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>34</v>
@@ -4148,22 +4113,22 @@
     </row>
     <row r="17" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>34</v>
@@ -4171,22 +4136,22 @@
     </row>
     <row r="18" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>34</v>
@@ -4194,22 +4159,22 @@
     </row>
     <row r="19" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>34</v>
@@ -4217,22 +4182,22 @@
     </row>
     <row r="20" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>34</v>
@@ -4240,22 +4205,22 @@
     </row>
     <row r="21" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>34</v>
@@ -4263,22 +4228,22 @@
     </row>
     <row r="22" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>34</v>
@@ -4286,22 +4251,22 @@
     </row>
     <row r="23" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>34</v>
@@ -4309,22 +4274,22 @@
     </row>
     <row r="24" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>34</v>
@@ -4332,22 +4297,22 @@
     </row>
     <row r="25" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>34</v>
@@ -4355,22 +4320,22 @@
     </row>
     <row r="26" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>34</v>
@@ -4378,22 +4343,22 @@
     </row>
     <row r="27" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>34</v>
@@ -4401,22 +4366,22 @@
     </row>
     <row r="28" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>34</v>
@@ -4424,22 +4389,22 @@
     </row>
     <row r="29" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>34</v>
@@ -4447,22 +4412,22 @@
     </row>
     <row r="30" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>34</v>
@@ -4470,22 +4435,22 @@
     </row>
     <row r="31" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>34</v>
@@ -4493,22 +4458,22 @@
     </row>
     <row r="32" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>34</v>
@@ -4522,16 +4487,16 @@
         <v>41</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>34</v>
@@ -4539,22 +4504,22 @@
     </row>
     <row r="34" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>34</v>
@@ -4568,23 +4533,23 @@
         <v>41</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G35" xr:uid="{82428735-F36E-4909-9AD5-47F1C98B3656}"/>
+  <autoFilter ref="A1:G35" xr:uid="{FD8E7D05-249C-4E1C-844F-D4D296C174CB}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/kintone-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/kintone-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51129893-D3B7-4F12-8029-DCC295E182A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B9ED296-B8FD-4A20-B77D-0AD1185D15D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2FEFC4D8-1CEF-4EBD-9C6C-E1B71B5C6001}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D64B4AA6-D274-4F3D-ACED-23E2FFE31DE1}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2.4 実行（アラート集計）'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2.5 実行（投稿）'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 ログ'!$A$1:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 環境設定（共通）'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 環境設定（共通）'!$A$1:$G$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'2.8 環境設定（グループ別）'!$A$1:$G$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（マスター）'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">一覧!$A$1:$C$10</definedName>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="340">
   <si>
     <t>通番</t>
   </si>
@@ -99,7 +99,7 @@
     <t>環境設定（共通）</t>
   </si>
   <si>
-    <t>32</t>
+    <t>30</t>
   </si>
   <si>
     <t>8</t>
@@ -420,11 +420,11 @@
     <t>メッセージ：「削除対象のログファイルがありません。」</t>
   </si>
   <si>
-    <t>基本設定：saved-client-data
+    <t>グループデータのフォルダ：saved-client-data
 設定ファイル：common.bat</t>
   </si>
   <si>
-    <t>「基本設定」を設定した後で、「保存」を押します。</t>
+    <t>「グループデータのフォルダ」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
     <t>設定ファイル：common.bat に saved-client-data が保存される
@@ -433,29 +433,6 @@
   <si>
     <t>画面設計：3.6
 処理フロー：2.8</t>
-  </si>
-  <si>
-    <t>基本設定：tmp-reload
-設定ファイル：common.bat</t>
-  </si>
-  <si>
-    <t>「基本設定」を設定した後で、「再読込」を押します。</t>
-  </si>
-  <si>
-    <t>基本設定：（保存されている値）
-変えた内容：消える
-状態（再読込）：完了</t>
-  </si>
-  <si>
-    <t>画面設計：3.6
-処理フロー：2.9</t>
-  </si>
-  <si>
-    <t>グループデータのフォルダ：saved-client-data
-設定ファイル：common.bat</t>
-  </si>
-  <si>
-    <t>「グループデータのフォルダ」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
     <t>グループデータのフォルダ：tmp-reload
@@ -470,6 +447,10 @@
 状態（再読込）：完了</t>
   </si>
   <si>
+    <t>画面設計：3.6
+処理フロー：2.9</t>
+  </si>
+  <si>
     <t>出力のルートフォルダ：saved-output-root
 設定ファイル：common.bat</t>
   </si>
@@ -527,9 +508,6 @@
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>ログの出力先：tmp-reload
 設定ファイル：common.bat</t>
   </si>
@@ -542,9 +520,6 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>提出状況の出力先：saved-report-output
 設定ファイル：common.bat</t>
   </si>
@@ -556,7 +531,7 @@
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>12</t>
+    <t>10</t>
   </si>
   <si>
     <t>提出状況の出力先：tmp-reload
@@ -571,7 +546,7 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>13</t>
+    <t>11</t>
   </si>
   <si>
     <t>アプリデータ集計の出力先：saved-collect-output
@@ -585,7 +560,7 @@
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>14</t>
+    <t>12</t>
   </si>
   <si>
     <t>アプリデータ集計の出力先：tmp-reload
@@ -600,7 +575,7 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>15</t>
+    <t>13</t>
   </si>
   <si>
     <t>アラート検知結果の出力先：saved-alert-output
@@ -614,7 +589,7 @@
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>16</t>
+    <t>14</t>
   </si>
   <si>
     <t>アラート検知結果の出力先：tmp-reload
@@ -629,7 +604,7 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>17</t>
+    <t>15</t>
   </si>
   <si>
     <t>バックアップの出力先：saved-backup-output
@@ -643,7 +618,7 @@
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>18</t>
+    <t>16</t>
   </si>
   <si>
     <t>バックアップの出力先：tmp-reload
@@ -658,7 +633,7 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>19</t>
+    <t>17</t>
   </si>
   <si>
     <t>業務日誌の日付フィールドコード：saved-daily-date
@@ -672,7 +647,7 @@
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>20</t>
+    <t>18</t>
   </si>
   <si>
     <t>業務日誌の日付フィールドコード：tmp-reload
@@ -687,7 +662,7 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>21</t>
+    <t>19</t>
   </si>
   <si>
     <t>業務日誌の受講生IDフィールドコード：saved-daily-user
@@ -701,7 +676,7 @@
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>22</t>
+    <t>20</t>
   </si>
   <si>
     <t>業務日誌の受講生IDフィールドコード：tmp-reload
@@ -716,7 +691,7 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>23</t>
+    <t>21</t>
   </si>
   <si>
     <t>パルスサーベイの日付フィールドコード：saved-pulse-date
@@ -730,7 +705,7 @@
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>24</t>
+    <t>22</t>
   </si>
   <si>
     <t>パルスサーベイの日付フィールドコード：tmp-reload
@@ -745,7 +720,7 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>25</t>
+    <t>23</t>
   </si>
   <si>
     <t>パルスサーベイの受講生IDフィールドコード：saved-pulse-user
@@ -759,7 +734,7 @@
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>26</t>
+    <t>24</t>
   </si>
   <si>
     <t>パルスサーベイの受講生IDフィールドコード：tmp-reload
@@ -774,7 +749,7 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>27</t>
+    <t>25</t>
   </si>
   <si>
     <t>アプリデータ集計の列定義：13行目
@@ -791,7 +766,7 @@
 処理フロー：2.10</t>
   </si>
   <si>
-    <t>28</t>
+    <t>26</t>
   </si>
   <si>
     <t>列定義（14行目）変更前：saved-col
@@ -809,7 +784,7 @@
 処理フロー：2.11</t>
   </si>
   <si>
-    <t>29</t>
+    <t>27</t>
   </si>
   <si>
     <t>列定義ファイル：collect-data-defs.json</t>
@@ -826,7 +801,7 @@
 処理フロー：2.8、2.10</t>
   </si>
   <si>
-    <t>30</t>
+    <t>28</t>
   </si>
   <si>
     <t>列定義（13行目）の変更後：saved-col
@@ -840,7 +815,7 @@
 状態（保存）：完了</t>
   </si>
   <si>
-    <t>31</t>
+    <t>29</t>
   </si>
   <si>
     <t>列定義（13行目）の変更後：tmp-reload
@@ -1254,6 +1229,9 @@
 グループ名：ok（既存のグループ名）</t>
   </si>
   <si>
+    <t>31</t>
+  </si>
+  <si>
     <t>対象のグループ：ok
 サブドメイン：空
 設定ファイル：ok.bat</t>
@@ -1264,6 +1242,9 @@
   <si>
     <t>メッセージ：「エラーが発生しました: サブドメイン・ログイン名・パスワードをすべて入力してください。」
 状態（認証情報）：失敗</t>
+  </si>
+  <si>
+    <t>32</t>
   </si>
   <si>
     <t>対象のグループ：ok
@@ -1775,7 +1756,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{501550C8-109F-40F0-9CCC-621C7510CA66}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8973BC1-0DF5-4926-A8A3-4C2D1FD16AE1}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1894,14 +1875,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10" xr:uid="{501550C8-109F-40F0-9CCC-621C7510CA66}"/>
+  <autoFilter ref="A1:C10" xr:uid="{F8973BC1-0DF5-4926-A8A3-4C2D1FD16AE1}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A1A3EA-EA03-4CB9-ADE0-1DF818399A72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AEBE0C8-FE81-4426-805D-E086BD036E5E}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1943,16 +1924,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -1966,16 +1947,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -1989,16 +1970,16 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -2012,16 +1993,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -2035,16 +2016,16 @@
         <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -2058,16 +2039,16 @@
         <v>41</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -2081,30 +2062,30 @@
         <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{86A1A3EA-EA03-4CB9-ADE0-1DF818399A72}"/>
+  <autoFilter ref="A1:G8" xr:uid="{8AEBE0C8-FE81-4426-805D-E086BD036E5E}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9633EDDE-2439-4D54-8946-C6EAF7CD4194}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CA5E741-32C6-4E48-9788-09BF0BB3340F}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2254,14 +2235,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{9633EDDE-2439-4D54-8946-C6EAF7CD4194}"/>
+  <autoFilter ref="A1:G6" xr:uid="{5CA5E741-32C6-4E48-9788-09BF0BB3340F}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BCD030D-3EFA-476E-9D6D-D3F11CD0E0CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B13BA6EA-654B-430A-AAA8-A73AAEB4C2A7}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2457,14 +2438,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{1BCD030D-3EFA-476E-9D6D-D3F11CD0E0CC}"/>
+  <autoFilter ref="A1:G8" xr:uid="{B13BA6EA-654B-430A-AAA8-A73AAEB4C2A7}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{962D8032-8D9E-46CD-AF9C-8ABFE96F93A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA1261BE-0865-46A8-B019-A2DF242711F8}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2568,14 +2549,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{962D8032-8D9E-46CD-AF9C-8ABFE96F93A5}"/>
+  <autoFilter ref="A1:G4" xr:uid="{BA1261BE-0865-46A8-B019-A2DF242711F8}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB9CBED-7A27-42BB-B63F-79191EE2E815}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76804136-90E6-4687-A2B8-30322E5B0289}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2679,14 +2660,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{2AB9CBED-7A27-42BB-B63F-79191EE2E815}"/>
+  <autoFilter ref="A1:G4" xr:uid="{76804136-90E6-4687-A2B8-30322E5B0289}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F17C32A5-93A6-4873-8A5C-1FAAD49C80FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049750E9-BB35-4B35-B0A7-3D878E7D4EDD}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2790,14 +2771,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{F17C32A5-93A6-4873-8A5C-1FAAD49C80FE}"/>
+  <autoFilter ref="A1:G4" xr:uid="{049750E9-BB35-4B35-B0A7-3D878E7D4EDD}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD14226C-85DF-4D3E-9BD3-13A6D76D0250}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D97A67E-7B21-45EA-9C19-ABF467A41FAC}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2947,15 +2928,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{CD14226C-85DF-4D3E-9BD3-13A6D76D0250}"/>
+  <autoFilter ref="A1:G6" xr:uid="{8D97A67E-7B21-45EA-9C19-ABF467A41FAC}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB437315-07BF-446C-9160-D5C8C02E30B4}">
-  <dimension ref="A1:G33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49155803-FBCD-4921-BFAE-ECEA0E0A098A}">
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
@@ -3011,7 +2992,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -3048,7 +3029,7 @@
         <v>104</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>98</v>
@@ -3065,13 +3046,13 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>102</v>
@@ -3088,13 +3069,13 @@
         <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>98</v>
@@ -3111,13 +3092,13 @@
         <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>102</v>
@@ -3134,13 +3115,13 @@
         <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>98</v>
@@ -3149,7 +3130,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -3157,13 +3138,13 @@
         <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>102</v>
@@ -3172,7 +3153,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -3180,13 +3161,13 @@
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>98</v>
@@ -3197,19 +3178,19 @@
     </row>
     <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>102</v>
@@ -3220,19 +3201,19 @@
     </row>
     <row r="12" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>98</v>
@@ -3241,21 +3222,21 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>102</v>
@@ -3266,19 +3247,19 @@
     </row>
     <row r="14" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>98</v>
@@ -3289,19 +3270,19 @@
     </row>
     <row r="15" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>102</v>
@@ -3312,19 +3293,19 @@
     </row>
     <row r="16" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>98</v>
@@ -3335,19 +3316,19 @@
     </row>
     <row r="17" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>102</v>
@@ -3358,19 +3339,19 @@
     </row>
     <row r="18" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>98</v>
@@ -3379,21 +3360,21 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>102</v>
@@ -3404,19 +3385,19 @@
     </row>
     <row r="20" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>98</v>
@@ -3427,19 +3408,19 @@
     </row>
     <row r="21" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>102</v>
@@ -3448,21 +3429,21 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>98</v>
@@ -3471,21 +3452,21 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>102</v>
@@ -3496,19 +3477,19 @@
     </row>
     <row r="24" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>98</v>
@@ -3519,19 +3500,19 @@
     </row>
     <row r="25" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>102</v>
@@ -3540,124 +3521,124 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F27" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A28" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A29" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A30" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="198" x14ac:dyDescent="0.45">
-      <c r="A28" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="270" x14ac:dyDescent="0.45">
-      <c r="A29" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="270" x14ac:dyDescent="0.45">
-      <c r="A30" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="G30" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>206</v>
+        <v>17</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>29</v>
@@ -3672,67 +3653,21 @@
         <v>209</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>205</v>
+        <v>102</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="234" x14ac:dyDescent="0.45">
-      <c r="A32" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="270" x14ac:dyDescent="0.45">
-      <c r="A33" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G33" xr:uid="{AB437315-07BF-446C-9160-D5C8C02E30B4}"/>
+  <autoFilter ref="A1:G31" xr:uid="{49155803-FBCD-4921-BFAE-ECEA0E0A098A}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD8E7D05-249C-4E1C-844F-D4D296C174CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7952C3B0-6576-404E-AF87-32797546DB18}">
   <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3774,16 +3709,16 @@
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>34</v>
@@ -3797,16 +3732,16 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
@@ -3820,16 +3755,16 @@
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>34</v>
@@ -3843,16 +3778,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -3866,16 +3801,16 @@
         <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -3889,16 +3824,16 @@
         <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -3912,16 +3847,16 @@
         <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
@@ -3935,16 +3870,16 @@
         <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
@@ -3958,16 +3893,16 @@
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
@@ -3975,22 +3910,22 @@
     </row>
     <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
@@ -3998,22 +3933,22 @@
     </row>
     <row r="12" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>34</v>
@@ -4021,22 +3956,22 @@
     </row>
     <row r="13" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>34</v>
@@ -4044,22 +3979,22 @@
     </row>
     <row r="14" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>34</v>
@@ -4067,22 +4002,22 @@
     </row>
     <row r="15" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>34</v>
@@ -4090,22 +4025,22 @@
     </row>
     <row r="16" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>34</v>
@@ -4113,22 +4048,22 @@
     </row>
     <row r="17" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>34</v>
@@ -4136,22 +4071,22 @@
     </row>
     <row r="18" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>34</v>
@@ -4159,22 +4094,22 @@
     </row>
     <row r="19" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>34</v>
@@ -4182,22 +4117,22 @@
     </row>
     <row r="20" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>34</v>
@@ -4205,22 +4140,22 @@
     </row>
     <row r="21" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>34</v>
@@ -4228,22 +4163,22 @@
     </row>
     <row r="22" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>34</v>
@@ -4251,22 +4186,22 @@
     </row>
     <row r="23" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>34</v>
@@ -4274,22 +4209,22 @@
     </row>
     <row r="24" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>34</v>
@@ -4297,22 +4232,22 @@
     </row>
     <row r="25" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>34</v>
@@ -4320,22 +4255,22 @@
     </row>
     <row r="26" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>34</v>
@@ -4343,22 +4278,22 @@
     </row>
     <row r="27" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>34</v>
@@ -4366,22 +4301,22 @@
     </row>
     <row r="28" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>34</v>
@@ -4389,22 +4324,22 @@
     </row>
     <row r="29" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>34</v>
@@ -4412,22 +4347,22 @@
     </row>
     <row r="30" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>34</v>
@@ -4435,22 +4370,22 @@
     </row>
     <row r="31" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>206</v>
+        <v>17</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>34</v>
@@ -4458,22 +4393,22 @@
     </row>
     <row r="32" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>210</v>
+        <v>306</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>34</v>
@@ -4481,22 +4416,22 @@
     </row>
     <row r="33" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>34</v>
@@ -4504,22 +4439,22 @@
     </row>
     <row r="34" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>34</v>
@@ -4533,23 +4468,23 @@
         <v>41</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G35" xr:uid="{FD8E7D05-249C-4E1C-844F-D4D296C174CB}"/>
+  <autoFilter ref="A1:G35" xr:uid="{7952C3B0-6576-404E-AF87-32797546DB18}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/kintone-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/kintone-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B9ED296-B8FD-4A20-B77D-0AD1185D15D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{221C9DD0-404F-46E0-BC76-1AE6D8F97A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D64B4AA6-D274-4F3D-ACED-23E2FFE31DE1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AB81CBD2-6547-41A3-8CB4-ED51CA866FBD}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -427,7 +427,7 @@
     <t>「グループデータのフォルダ」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-client-data が保存される
+    <t>設定ファイル：common.bat に ClientDataRootDir=saved-client-data が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -458,7 +458,7 @@
     <t>「出力のルートフォルダ」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-output-root が保存される
+    <t>設定ファイル：common.bat に OutputRootDir=saved-output-root が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -481,7 +481,7 @@
     <t>「テンプレートのフォルダ」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-template が保存される
+    <t>設定ファイル：common.bat に TemplateRootDir=saved-template が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -504,7 +504,7 @@
     <t>「ログの出力先」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-log-path が保存される
+    <t>設定ファイル：common.bat に CommonLogPath=saved-log-path が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -527,7 +527,7 @@
     <t>「提出状況の出力先」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-report-output が保存される
+    <t>設定ファイル：common.bat に OutputReportDir=saved-report-output が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -556,7 +556,7 @@
     <t>「アプリデータ集計の出力先」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-collect-output が保存される
+    <t>設定ファイル：common.bat に OutputCollectDataRootDir=saved-collect-output が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -585,7 +585,7 @@
     <t>「アラート検知結果の出力先」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-alert-output が保存される
+    <t>設定ファイル：common.bat に OutputAlertRootDir=saved-alert-output が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -614,7 +614,7 @@
     <t>「バックアップの出力先」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-backup-output が保存される
+    <t>設定ファイル：common.bat に OutputAlertBackupDir=saved-backup-output が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -643,7 +643,7 @@
     <t>「業務日誌の日付フィールドコード」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-daily-date が保存される
+    <t>設定ファイル：common.bat に TargetDateCodeFieldDaily=saved-daily-date が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -672,7 +672,7 @@
     <t>「業務日誌の受講生IDフィールドコード」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-daily-user が保存される
+    <t>設定ファイル：common.bat に TargetUserCodeFieldDaily=saved-daily-user が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -701,7 +701,7 @@
     <t>「パルスサーベイの日付フィールドコード」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-pulse-date が保存される
+    <t>設定ファイル：common.bat に TargetDateCodeFieldPulse=saved-pulse-date が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -730,7 +730,7 @@
     <t>「パルスサーベイの受講生IDフィールドコード」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-pulse-user が保存される
+    <t>設定ファイル：common.bat に TargetUserCodeFieldPulse=saved-pulse-user が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -776,7 +776,7 @@
     <t>「追加（アプリデータ集計の列定義）」を押した後で、「変更前」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>表：末尾に行が追加される（未確認）、入力した値が collect-data-defs.json に保存される
+    <t>入力した値が collect-data-defs.json に保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -1341,7 +1341,7 @@
     <t>「対象のグループ」を設定した後で、「追加（スケジュール）」を押します。</t>
   </si>
   <si>
-    <t>表：末尾に2行目が追加される（未確認）、通番は2になる</t>
+    <t>表：末尾に行が追加される</t>
   </si>
   <si>
     <t>画面設計：3.8
@@ -1756,7 +1756,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8973BC1-0DF5-4926-A8A3-4C2D1FD16AE1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF18E502-EF3B-4C1D-BD5F-CECD2899EEB2}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1875,14 +1875,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10" xr:uid="{F8973BC1-0DF5-4926-A8A3-4C2D1FD16AE1}"/>
+  <autoFilter ref="A1:C10" xr:uid="{EF18E502-EF3B-4C1D-BD5F-CECD2899EEB2}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AEBE0C8-FE81-4426-805D-E086BD036E5E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7B5BAC-3FD8-4EE6-9250-69F314BC2ECA}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2078,14 +2078,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{8AEBE0C8-FE81-4426-805D-E086BD036E5E}"/>
+  <autoFilter ref="A1:G8" xr:uid="{8F7B5BAC-3FD8-4EE6-9250-69F314BC2ECA}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CA5E741-32C6-4E48-9788-09BF0BB3340F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{114103D9-82DA-40E5-8370-8280B1D120A0}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2235,14 +2235,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{5CA5E741-32C6-4E48-9788-09BF0BB3340F}"/>
+  <autoFilter ref="A1:G6" xr:uid="{114103D9-82DA-40E5-8370-8280B1D120A0}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B13BA6EA-654B-430A-AAA8-A73AAEB4C2A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9E30BCD-1B9F-410E-85C3-547DFCB9A97C}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2438,14 +2438,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{B13BA6EA-654B-430A-AAA8-A73AAEB4C2A7}"/>
+  <autoFilter ref="A1:G8" xr:uid="{F9E30BCD-1B9F-410E-85C3-547DFCB9A97C}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA1261BE-0865-46A8-B019-A2DF242711F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176F727B-D7F6-4917-AE13-11CBA99B385B}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2549,14 +2549,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{BA1261BE-0865-46A8-B019-A2DF242711F8}"/>
+  <autoFilter ref="A1:G4" xr:uid="{176F727B-D7F6-4917-AE13-11CBA99B385B}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76804136-90E6-4687-A2B8-30322E5B0289}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3445EB-EEE7-4171-A657-DD07386FAAE0}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2660,14 +2660,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{76804136-90E6-4687-A2B8-30322E5B0289}"/>
+  <autoFilter ref="A1:G4" xr:uid="{7E3445EB-EEE7-4171-A657-DD07386FAAE0}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049750E9-BB35-4B35-B0A7-3D878E7D4EDD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{550974BC-43BE-40B7-AFD6-83F3B232BC4C}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2771,14 +2771,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{049750E9-BB35-4B35-B0A7-3D878E7D4EDD}"/>
+  <autoFilter ref="A1:G4" xr:uid="{550974BC-43BE-40B7-AFD6-83F3B232BC4C}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D97A67E-7B21-45EA-9C19-ABF467A41FAC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED7526B-8259-4227-B93F-304B745D6EED}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2928,14 +2928,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{8D97A67E-7B21-45EA-9C19-ABF467A41FAC}"/>
+  <autoFilter ref="A1:G6" xr:uid="{CED7526B-8259-4227-B93F-304B745D6EED}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49155803-FBCD-4921-BFAE-ECEA0E0A098A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B441B24B-81E5-4BA2-8E70-D6C630E1B399}">
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2969,7 +2969,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>128</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>136</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>144</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
         <v>152</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>160</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>168</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>176</v>
       </c>
@@ -3544,7 +3544,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
         <v>189</v>
       </c>
@@ -3660,14 +3660,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G31" xr:uid="{49155803-FBCD-4921-BFAE-ECEA0E0A098A}"/>
+  <autoFilter ref="A1:G31" xr:uid="{B441B24B-81E5-4BA2-8E70-D6C630E1B399}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7952C3B0-6576-404E-AF87-32797546DB18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F56F55E6-5035-4E36-96D9-163390394668}">
   <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4484,7 +4484,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G35" xr:uid="{7952C3B0-6576-404E-AF87-32797546DB18}"/>
+  <autoFilter ref="A1:G35" xr:uid="{F56F55E6-5035-4E36-96D9-163390394668}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/kintone-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/kintone-aggregator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{221C9DD0-404F-46E0-BC76-1AE6D8F97A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2999FAF-4919-4D0D-B119-272B52C3D7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AB81CBD2-6547-41A3-8CB4-ED51CA866FBD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2D903901-D8C4-4FEA-BF24-60BDBCF36F7C}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 ログ'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 環境設定（共通）'!$A$1:$G$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'2.8 環境設定（グループ別）'!$A$1:$G$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（マスター）'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（マスター）'!$A$1:$G$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">一覧!$A$1:$C$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="349">
   <si>
     <t>通番</t>
   </si>
@@ -115,6 +115,9 @@
   </si>
   <si>
     <t>環境設定（マスター）</t>
+  </si>
+  <si>
+    <t>11</t>
   </si>
   <si>
     <t>区分</t>
@@ -546,9 +549,6 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>アプリデータ集計の出力先：saved-collect-output
 設定ファイル：common.bat</t>
   </si>
@@ -859,7 +859,7 @@
   <si>
     <t>対象のグループ：ok
 設定ファイル：ok.bat
-Excel ファイル：ok.xlsx
+定義ファイル：ok.xlsx
 グループ名：TestCopy</t>
   </si>
   <si>
@@ -868,7 +868,7 @@
   <si>
     <t>一覧：TestCopy が選ばれる
 設定ファイル：TestCopy.bat
-Excel ファイル：TestCopy.xlsx</t>
+定義ファイル：TestCopy.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.7
@@ -912,7 +912,7 @@
     <t>「対象のグループ」と「サブドメイン」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat に saved-subdomain が保存される
+    <t>設定ファイル：ok.bat に KintoneSubdomain=saved-subdomain が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -938,14 +938,14 @@
   </si>
   <si>
     <t>対象のグループ：ok
-ログイン名：テスト用の値
+ログイン名：saved-login-name
 設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象のグループ」と「ログイン名」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat の KintoneLoginName が保存される
+    <t>設定ファイル：ok.bat に KintoneLoginName=saved-login-name が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -963,14 +963,14 @@
   </si>
   <si>
     <t>対象のグループ：ok
-パスワード：テスト用の値
+パスワード：saved-pass
 設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象のグループ」と「パスワード」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat の KintonePassword が保存される
+    <t>設定ファイル：ok.bat に KintonePassword=saved-pass が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -982,7 +982,7 @@
     <t>「対象のグループ」と「投稿先スペースID」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat に saved-space-id が保存される
+    <t>設定ファイル：ok.bat に SpaceId=saved-space-id が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -1007,7 +1007,7 @@
     <t>「対象のグループ」と「投稿先スレッドID」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat に saved-thread-id が保存される
+    <t>設定ファイル：ok.bat に ThreadId=saved-thread-id が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -1032,7 +1032,7 @@
     <t>「対象のグループ」と「投稿コメント文言」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat に saved-comment が保存される
+    <t>設定ファイル：ok.bat に CommentTextTemplate=saved-comment が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -1057,7 +1057,7 @@
     <t>「対象のグループ」と「投稿集計文言」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat に saved-summary が保存される
+    <t>設定ファイル：ok.bat に CommentSummaryTemplate=saved-summary が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -1097,7 +1097,7 @@
     <t>「対象のグループ」と「対象アプリID（ユーザー）」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat に saved-user-app が保存される
+    <t>設定ファイル：ok.bat に SyncUserMasterAppId=saved-user-app が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -1137,7 +1137,7 @@
     <t>「対象のグループ」と「対象アプリID（業務日誌）」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat に saved-daily-app が保存される
+    <t>設定ファイル：ok.bat に DailyTargetAppIds=saved-daily-app が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -1177,7 +1177,7 @@
     <t>「対象のグループ」と「対象アプリID（パルスサーベイ）」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat に saved-pulse-app が保存される
+    <t>設定ファイル：ok.bat に PulseTargetAppIds=saved-pulse-app が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -1220,12 +1220,12 @@
     <t>「対象のグループ」を設定した後で、「新規作成」を押した後で、「キャンセル」を押します。</t>
   </si>
   <si>
-    <t>ファイル：TestCancel.bat が作られない</t>
+    <t>設定ファイル：TestCancel.bat が作られない</t>
   </si>
   <si>
     <t>対象のグループ：ok
 設定ファイル：ok.bat
-Excel ファイル：ok.xlsx
+定義ファイル：ok.xlsx
 グループ名：ok（既存のグループ名）</t>
   </si>
   <si>
@@ -1282,51 +1282,84 @@
 状態（業務日誌）：失敗</t>
   </si>
   <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat
+定義ファイル：ok.xlsx</t>
+  </si>
+  <si>
     <t>「対象のグループ」を設定した後で、「同期実行」を押します。</t>
   </si>
   <si>
-    <t>状態（同期実行）：成功</t>
+    <t>状態（同期実行）：成功
+Excelファイル：ok.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.8
 処理フロー：2.23</t>
   </si>
   <si>
-    <t>「対象のグループ」を設定した後で、スケジュールの1行目の「削除（スケジュール）」を押した後で、「保存」を押します。</t>
-  </si>
-  <si>
-    <t>表：その行が削除される
+    <t>「対象のグループ」を設定した後で、「追加（スケジュール）」を押します。</t>
+  </si>
+  <si>
+    <t>スケジュールの通番（2行目）：2
+スケジュールの科目名（2行目）：空</t>
+  </si>
+  <si>
+    <t>画面設計：3.8</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「削除（スケジュールの1行目）」を押します。</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+科目名（1行目）：saved-subject
+設定ファイル：ok.bat
+定義ファイル：ok.xlsx</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スケジュールの科目名（1行目）」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>スケジュールの科目名（1行目）：saved-subject が表示される
 状態（保存）：完了
-ファイル：ok.xlsx のスケジュールの科目名（1行目）が空になる</t>
-  </si>
-  <si>
-    <t>画面設計：3.8
-処理フロー：2.24</t>
+Excelファイル：ok.xlsx</t>
   </si>
   <si>
     <t>対象のグループ：ok
-科目名：saved-subject
-設定ファイル：ok.bat</t>
-  </si>
-  <si>
-    <t>「対象のグループ」を設定し、スケジュールの1行目の「科目名」を設定した後で、「保存」を押します。</t>
-  </si>
-  <si>
-    <t>画面の表示：保存後の内容（saved-subject）が表示される
+開始日（1行目）：saved-start-date
+設定ファイル：ok.bat
+定義ファイル：ok.xlsx</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スケジュールの開始日（1行目）」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>スケジュールの開始日（1行目）：saved-start-date が表示される
 状態（保存）：完了
-ファイル：ok.xlsx のスケジュールの科目名（1行目）が saved-subject になる</t>
-  </si>
-  <si>
-    <t>画面設計：3.8
-処理フロー：2.21</t>
+Excelファイル：ok.xlsx</t>
   </si>
   <si>
     <t>対象のグループ：ok
-科目名：tmp-reload
-設定ファイル：ok.bat</t>
-  </si>
-  <si>
-    <t>「対象のグループ」を設定し、スケジュールの1行目の「科目名」を設定した後で、「再読込」を押します。</t>
+終了日（1行目）：saved-end-date
+設定ファイル：ok.bat
+定義ファイル：ok.xlsx</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スケジュールの終了日（1行目）」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>スケジュールの終了日（1行目）：saved-end-date が表示される
+状態（保存）：完了
+Excelファイル：ok.xlsx</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+科目名（1行目）：tmp-reload
+設定ファイル：ok.bat
+定義ファイル：ok.xlsx</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スケジュールの科目名（1行目）」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
     <t>スケジュールの科目名（1行目）：（保存されている値）
@@ -1334,30 +1367,44 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>画面設計：3.8
-処理フロー：2.22</t>
-  </si>
-  <si>
-    <t>「対象のグループ」を設定した後で、「追加（スケジュール）」を押します。</t>
-  </si>
-  <si>
-    <t>表：末尾に行が追加される</t>
-  </si>
-  <si>
-    <t>画面設計：3.8
-処理フロー：2.25</t>
+    <t>対象のグループ：ok
+開始日（1行目）：tmp-reload
+設定ファイル：ok.bat
+定義ファイル：ok.xlsx</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スケジュールの開始日（1行目）」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>スケジュールの開始日（1行目）：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+終了日（1行目）：tmp-reload
+設定ファイル：ok.bat
+定義ファイル：ok.xlsx</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スケジュールの終了日（1行目）」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>スケジュールの終了日（1行目）：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
   </si>
   <si>
     <t>対象のグループ：ng
-設定ファイル：ng.bat</t>
+設定ファイル：ng.bat
+定義ファイル：ng.xlsx</t>
   </si>
   <si>
     <t>状態（同期実行）：失敗</t>
   </si>
   <si>
     <t>メッセージ：「エラーが発生しました: 対象アプリIDが設定されていません。」
-状態（同期実行）：失敗
-ユーザーマスター：書き込まれない（未確認）</t>
+状態（同期実行）：失敗</t>
   </si>
 </sst>
 </file>
@@ -1756,7 +1803,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF18E502-EF3B-4C1D-BD5F-CECD2899EEB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9611CC58-CAA1-4849-B664-D434A57AB779}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1871,18 +1918,470 @@
         <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10" xr:uid="{EF18E502-EF3B-4C1D-BD5F-CECD2899EEB2}"/>
+  <autoFilter ref="A1:C10" xr:uid="{9611CC58-CAA1-4849-B664-D434A57AB779}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7B5BAC-3FD8-4EE6-9250-69F314BC2ECA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12761A61-6707-41CD-8D8D-17C23CDD6B54}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G12" xr:uid="{12761A61-6707-41CD-8D8D-17C23CDD6B54}"/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0FBA802-29E1-4DE8-87F8-9428FF7FFE80}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G6" xr:uid="{F0FBA802-29E1-4DE8-87F8-9428FF7FFE80}"/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70C7D335-BB17-4EA6-ACFF-03B139FF31CA}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1898,194 +2397,527 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>302</v>
+        <v>47</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>320</v>
+        <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>321</v>
+        <v>49</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>322</v>
+        <v>50</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>302</v>
+        <v>47</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>323</v>
+        <v>51</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>324</v>
+        <v>52</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>325</v>
+        <v>53</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="378" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>326</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>327</v>
+        <v>54</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>328</v>
+        <v>55</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>329</v>
+        <v>56</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>330</v>
+        <v>47</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>331</v>
+        <v>57</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>332</v>
+        <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>333</v>
+        <v>53</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>302</v>
+        <v>58</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>334</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>335</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>336</v>
+        <v>50</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>337</v>
+        <v>59</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>320</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>338</v>
+        <v>60</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>322</v>
+        <v>50</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="342" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>337</v>
+        <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>320</v>
+        <v>54</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>339</v>
+        <v>61</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>322</v>
+        <v>56</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{8F7B5BAC-3FD8-4EE6-9250-69F314BC2ECA}"/>
+  <autoFilter ref="A1:G8" xr:uid="{70C7D335-BB17-4EA6-ACFF-03B139FF31CA}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{114103D9-82DA-40E5-8370-8280B1D120A0}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E7031B0-7D04-47AC-925A-947E36894355}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G4" xr:uid="{8E7031B0-7D04-47AC-925A-947E36894355}"/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D941232B-13FA-4649-972B-DD6929710BB9}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="360" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G4" xr:uid="{D941232B-13FA-4649-972B-DD6929710BB9}"/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F46C282B-554D-45CE-9E9E-73C5FD6B1A63}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="342" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="342" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G4" xr:uid="{F46C282B-554D-45CE-9E9E-73C5FD6B1A63}"/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D98753F2-DA10-43BE-A78F-4D154314C64A}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2101,91 +2933,91 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
@@ -2193,715 +3025,22 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{114103D9-82DA-40E5-8370-8280B1D120A0}"/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9E30BCD-1B9F-410E-85C3-547DFCB9A97C}">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="5" width="70.69921875" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" customWidth="1"/>
-    <col min="7" max="7" width="12.69921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="288" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="216" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="306" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="198" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="216" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G8" xr:uid="{F9E30BCD-1B9F-410E-85C3-547DFCB9A97C}"/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176F727B-D7F6-4917-AE13-11CBA99B385B}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="5" width="70.69921875" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" customWidth="1"/>
-    <col min="7" max="7" width="12.69921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="288" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="288" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{176F727B-D7F6-4917-AE13-11CBA99B385B}"/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3445EB-EEE7-4171-A657-DD07386FAAE0}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="5" width="70.69921875" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" customWidth="1"/>
-    <col min="7" max="7" width="12.69921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="360" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{7E3445EB-EEE7-4171-A657-DD07386FAAE0}"/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{550974BC-43BE-40B7-AFD6-83F3B232BC4C}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="5" width="70.69921875" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" customWidth="1"/>
-    <col min="7" max="7" width="12.69921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="342" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="342" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{550974BC-43BE-40B7-AFD6-83F3B232BC4C}"/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED7526B-8259-4227-B93F-304B745D6EED}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="5" width="70.69921875" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" customWidth="1"/>
-    <col min="7" max="7" width="12.69921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="270" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="252" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -2909,33 +3048,33 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{CED7526B-8259-4227-B93F-304B745D6EED}"/>
+  <autoFilter ref="A1:G6" xr:uid="{D98753F2-DA10-43BE-A78F-4D154314C64A}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B441B24B-81E5-4BA2-8E70-D6C630E1B399}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5714885-2774-4B46-818B-3F0D42EEBEE4}">
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2951,22 +3090,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -2974,22 +3113,22 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -2997,22 +3136,22 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -3020,22 +3159,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -3043,22 +3182,22 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -3066,22 +3205,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -3089,22 +3228,22 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -3112,22 +3251,22 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -3135,22 +3274,22 @@
         <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="252" x14ac:dyDescent="0.45">
@@ -3158,53 +3297,53 @@
         <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>128</v>
+        <v>23</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>129</v>
@@ -3216,10 +3355,10 @@
         <v>131</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -3227,7 +3366,7 @@
         <v>132</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>133</v>
@@ -3239,10 +3378,10 @@
         <v>135</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="252" x14ac:dyDescent="0.45">
@@ -3250,7 +3389,7 @@
         <v>136</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>137</v>
@@ -3262,10 +3401,10 @@
         <v>139</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -3273,7 +3412,7 @@
         <v>140</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>141</v>
@@ -3285,10 +3424,10 @@
         <v>143</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="270" x14ac:dyDescent="0.45">
@@ -3296,7 +3435,7 @@
         <v>144</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>145</v>
@@ -3308,10 +3447,10 @@
         <v>147</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -3319,7 +3458,7 @@
         <v>148</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>149</v>
@@ -3331,10 +3470,10 @@
         <v>151</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="252" x14ac:dyDescent="0.45">
@@ -3342,7 +3481,7 @@
         <v>152</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>153</v>
@@ -3354,10 +3493,10 @@
         <v>155</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -3365,7 +3504,7 @@
         <v>156</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>157</v>
@@ -3377,10 +3516,10 @@
         <v>159</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="252" x14ac:dyDescent="0.45">
@@ -3388,7 +3527,7 @@
         <v>160</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>161</v>
@@ -3400,10 +3539,10 @@
         <v>163</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -3411,7 +3550,7 @@
         <v>164</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>165</v>
@@ -3423,10 +3562,10 @@
         <v>167</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="252" x14ac:dyDescent="0.45">
@@ -3434,7 +3573,7 @@
         <v>168</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>169</v>
@@ -3446,10 +3585,10 @@
         <v>171</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="252" x14ac:dyDescent="0.45">
@@ -3457,7 +3596,7 @@
         <v>172</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>173</v>
@@ -3469,10 +3608,10 @@
         <v>175</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="252" x14ac:dyDescent="0.45">
@@ -3480,7 +3619,7 @@
         <v>176</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>177</v>
@@ -3492,10 +3631,10 @@
         <v>179</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="252" x14ac:dyDescent="0.45">
@@ -3503,7 +3642,7 @@
         <v>180</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>181</v>
@@ -3515,10 +3654,10 @@
         <v>183</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -3526,7 +3665,7 @@
         <v>184</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>185</v>
@@ -3541,7 +3680,7 @@
         <v>188</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -3549,7 +3688,7 @@
         <v>189</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>190</v>
@@ -3564,7 +3703,7 @@
         <v>193</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="270" x14ac:dyDescent="0.45">
@@ -3572,7 +3711,7 @@
         <v>194</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>195</v>
@@ -3587,7 +3726,7 @@
         <v>198</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -3595,7 +3734,7 @@
         <v>199</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>200</v>
@@ -3610,7 +3749,7 @@
         <v>198</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -3618,7 +3757,7 @@
         <v>203</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>204</v>
@@ -3630,10 +3769,10 @@
         <v>206</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="270" x14ac:dyDescent="0.45">
@@ -3641,7 +3780,7 @@
         <v>17</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>207</v>
@@ -3653,21 +3792,21 @@
         <v>209</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G31" xr:uid="{B441B24B-81E5-4BA2-8E70-D6C630E1B399}"/>
+  <autoFilter ref="A1:G31" xr:uid="{D5714885-2774-4B46-818B-3F0D42EEBEE4}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F56F55E6-5035-4E36-96D9-163390394668}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB1293AB-9BBF-4493-88C3-78CAD8C9A9CB}">
   <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3683,22 +3822,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -3706,7 +3845,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>210</v>
@@ -3721,7 +3860,7 @@
         <v>213</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -3729,7 +3868,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>214</v>
@@ -3744,7 +3883,7 @@
         <v>217</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -3752,7 +3891,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>218</v>
@@ -3767,7 +3906,7 @@
         <v>221</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="180" x14ac:dyDescent="0.45">
@@ -3775,7 +3914,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>222</v>
@@ -3790,15 +3929,15 @@
         <v>225</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>226</v>
@@ -3813,7 +3952,7 @@
         <v>229</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -3821,7 +3960,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>230</v>
@@ -3836,15 +3975,15 @@
         <v>233</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>234</v>
@@ -3859,7 +3998,7 @@
         <v>229</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="180" x14ac:dyDescent="0.45">
@@ -3867,7 +4006,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>237</v>
@@ -3882,15 +4021,15 @@
         <v>221</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>240</v>
@@ -3905,15 +4044,15 @@
         <v>229</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>243</v>
@@ -3928,15 +4067,15 @@
         <v>229</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>128</v>
+        <v>23</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>246</v>
@@ -3951,7 +4090,7 @@
         <v>221</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -3959,7 +4098,7 @@
         <v>132</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>249</v>
@@ -3974,7 +4113,7 @@
         <v>229</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -3982,7 +4121,7 @@
         <v>136</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>252</v>
@@ -3997,15 +4136,15 @@
         <v>221</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>140</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>255</v>
@@ -4020,7 +4159,7 @@
         <v>229</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -4028,7 +4167,7 @@
         <v>144</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>258</v>
@@ -4043,15 +4182,15 @@
         <v>221</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
         <v>148</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>261</v>
@@ -4066,7 +4205,7 @@
         <v>229</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="198" x14ac:dyDescent="0.45">
@@ -4074,7 +4213,7 @@
         <v>152</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>264</v>
@@ -4089,7 +4228,7 @@
         <v>221</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="270" x14ac:dyDescent="0.45">
@@ -4097,7 +4236,7 @@
         <v>156</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>267</v>
@@ -4112,7 +4251,7 @@
         <v>270</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -4120,7 +4259,7 @@
         <v>160</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>271</v>
@@ -4135,7 +4274,7 @@
         <v>229</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -4143,7 +4282,7 @@
         <v>164</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>274</v>
@@ -4158,7 +4297,7 @@
         <v>221</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="270" x14ac:dyDescent="0.45">
@@ -4166,7 +4305,7 @@
         <v>168</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>277</v>
@@ -4181,7 +4320,7 @@
         <v>280</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -4189,7 +4328,7 @@
         <v>172</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>281</v>
@@ -4204,7 +4343,7 @@
         <v>229</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -4212,7 +4351,7 @@
         <v>176</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>284</v>
@@ -4227,7 +4366,7 @@
         <v>221</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="288" x14ac:dyDescent="0.45">
@@ -4235,7 +4374,7 @@
         <v>180</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>287</v>
@@ -4250,7 +4389,7 @@
         <v>290</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -4258,7 +4397,7 @@
         <v>184</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>291</v>
@@ -4273,7 +4412,7 @@
         <v>229</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -4281,7 +4420,7 @@
         <v>189</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>294</v>
@@ -4296,7 +4435,7 @@
         <v>221</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -4304,7 +4443,7 @@
         <v>194</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>297</v>
@@ -4319,7 +4458,7 @@
         <v>213</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="288" x14ac:dyDescent="0.45">
@@ -4327,7 +4466,7 @@
         <v>199</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>299</v>
@@ -4342,7 +4481,7 @@
         <v>217</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="216" x14ac:dyDescent="0.45">
@@ -4350,7 +4489,7 @@
         <v>203</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>302</v>
@@ -4365,15 +4504,15 @@
         <v>213</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>305</v>
@@ -4388,7 +4527,7 @@
         <v>217</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="306" x14ac:dyDescent="0.45">
@@ -4396,7 +4535,7 @@
         <v>306</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>307</v>
@@ -4411,7 +4550,7 @@
         <v>221</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="234" x14ac:dyDescent="0.45">
@@ -4419,7 +4558,7 @@
         <v>310</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>311</v>
@@ -4434,7 +4573,7 @@
         <v>221</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="270" x14ac:dyDescent="0.45">
@@ -4442,7 +4581,7 @@
         <v>314</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>315</v>
@@ -4457,7 +4596,7 @@
         <v>225</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="270" x14ac:dyDescent="0.45">
@@ -4465,7 +4604,7 @@
         <v>20</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>318</v>
@@ -4480,11 +4619,11 @@
         <v>280</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G35" xr:uid="{F56F55E6-5035-4E36-96D9-163390394668}"/>
+  <autoFilter ref="A1:G35" xr:uid="{BB1293AB-9BBF-4493-88C3-78CAD8C9A9CB}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
